--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -903,12 +903,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1019,67 +1019,67 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC2" t="n">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1450,67 +1450,67 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC3" t="n">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1871,7 +1871,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1881,67 +1881,67 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
+          <t>-3.962489301787693</t>
         </is>
       </c>
       <c r="BC4" t="n">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,7 +2302,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-103.19</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.775715126621417</t>
+          <t>-3.87688447150315</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -2475,27 +2475,27 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,39 +2602,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5.15</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-27.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,7 +2733,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2743,67 +2743,67 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.656151355397551</t>
+          <t>-3.775715126621417</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>3.58</v>
+        <v>-4.43</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-11.30</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-7.35</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4.971948157141623</t>
+          <t>-3.656151355397551</t>
         </is>
       </c>
       <c r="BC7" t="n">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,7 +3595,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>24.33</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
           <t>25.73</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.60</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6.526980741020981</t>
+          <t>-4.971948157141623</t>
         </is>
       </c>
       <c r="BC8" t="n">
@@ -3768,27 +3768,27 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,7 +4026,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4036,67 +4036,67 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>80.06</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-104.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,11 +4146,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.364746521969312</t>
+          <t>-6.526980741020981</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>2.19</v>
+        <v>3.58</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-11.30</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,7 +4457,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4467,67 +4467,67 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>94.57</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-9.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.01</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>80.06</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.39</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4577,11 +4577,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10.28404023044595</t>
+          <t>-8.364746521969312</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>9.24</v>
+        <v>2.19</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,17 +4630,17 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.7</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-18.53</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,7 +4888,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4898,67 +4898,67 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.57</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>71.34</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.40</t>
+          <t>-106.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13.83303762581209</t>
+          <t>-10.28404023044595</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-7.71</v>
+        <v>9.24</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,39 +5188,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>9.74</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-11.24</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>23.35</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>7.52</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-31.32</t>
+          <t>-18.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>19.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5329,67 +5329,67 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>64.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>71.34</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.02</t>
+          <t>-107.40</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-14.94631777704066</t>
+          <t>-13.83303762581209</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.57</v>
+        <v>-7.71</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-13.52</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-41.74757281553398</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>9900.0</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1672.0</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>821</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,22 +5840,22 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>792.6</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -5865,16 +5865,16 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>23.51</v>
+        <v>-26.14</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,22 +5923,22 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,22 +6271,22 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>867.2</t>
+          <t>792.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -6296,16 +6296,16 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-9.58</v>
+        <v>23.51</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,32 +6354,32 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,131 +6612,131 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>40.37</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>43.23</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>43.79</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-24.22</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-162.38</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>1663.301886792453</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>867.2</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>999.8</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-29.93</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-158.60</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>1665.111191860465</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>579.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>1050.4</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
+          <t>54.97412508298164</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>59.52</v>
+        <v>-9.58</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,32 +6785,32 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-154.22</t>
+          <t>-158.60</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,22 +7133,22 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1291.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1329.8</t>
+          <t>975.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1069.9</t>
+          <t>1050.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -7158,16 +7158,16 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>68.01783797577676</t>
+          <t>66.71115149108003</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>111.12</v>
+        <v>59.52</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,32 +7216,32 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>43.42</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-31.21</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-149.99</t>
+          <t>-154.22</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,22 +7564,22 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>1291.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1265.6</t>
+          <t>1329.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1069.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -7589,16 +7589,16 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>60.18138003141154</t>
+          <t>68.01783797577676</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>104.57</v>
+        <v>111.12</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,32 +7647,32 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>41.65</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-146.23</t>
+          <t>-149.99</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,17 +7995,17 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1615.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1421.2</t>
+          <t>1265.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -8025,11 +8025,11 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>52.1107552068259</t>
+          <t>60.18138003141154</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>155.66</v>
+        <v>104.57</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-14.52</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,17 +8078,17 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>42.57</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-25.52</t>
+          <t>-23.64</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-143.50</t>
+          <t>-146.23</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,17 +8426,17 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>1615.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1132.4</t>
+          <t>1421.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -8456,11 +8456,11 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>33.28385717187894</t>
+          <t>52.1107552068259</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>124.19</v>
+        <v>155.66</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8509,27 +8509,27 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-21.67</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.92999999999999</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.66</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-25.52</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-140.72</t>
+          <t>-143.50</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,17 +8857,17 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1125.2</t>
+          <t>1132.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -8887,11 +8887,11 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>16.75533859228556</t>
+          <t>33.28385717187894</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>172.73</v>
+        <v>124.19</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-14.52</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,32 +8940,32 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-20.72</t>
+          <t>-21.48</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,17 +9218,17 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9238,37 +9238,37 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.92999999999999</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-138.27</t>
+          <t>-140.72</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,17 +9288,17 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>970.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>810.0</t>
+          <t>1125.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -9318,11 +9318,11 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-11.60362420349809</t>
+          <t>16.75533859228556</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>59.22</v>
+        <v>172.73</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-20.72</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>43.06</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-136.46</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,29 +9719,29 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1665.111191860465</t>
+          <t>1663.301886792453</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1470.0</t>
+          <t>970.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
+          <t>810.0</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA22" t="inlineStr">
         <is>
           <t>0</t>
@@ -9749,11 +9749,11 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-24.48127731545686</t>
+          <t>-11.60362420349809</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>42.81</v>
+        <v>59.22</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-12.24</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.87</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>2.92</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>-2.25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,119 +10060,119 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>14.29</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>42.34</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>43.06</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>44.31</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-136.46</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>1663.301886792453</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>1470.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-1.77</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>42.41</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>43.17</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>43.89</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-19.41</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-135.11</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>1665.111191860465</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA23" t="inlineStr">
         <is>
           <t>0</t>
@@ -10180,11 +10180,11 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-36.71674975825822</t>
+          <t>-24.48127731545686</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-35.73</v>
+        <v>42.81</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-12.55</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>4.911621841208736</t>
+          <t>5.61175015634552</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>3.787357422154609</t>
+          <t>2.720079552075342</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>2.478625081422838</t>
+          <t>2.597352307479901</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-4.43</v>
+        <v>-1.98</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC3" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC4" t="n">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
+          <t>-3.962489301787693</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-103.19</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.775715126621417</t>
+          <t>-3.87688447150315</t>
         </is>
       </c>
       <c r="BC6" t="n">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-27.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3.656151355397551</t>
+          <t>-3.775715126621417</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>3.58</v>
+        <v>-4.43</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-11.30</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-7.35</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4.971948157141623</t>
+          <t>-3.656151355397551</t>
         </is>
       </c>
       <c r="BC8" t="n">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>24.33</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
           <t>25.73</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.60</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6.526980741020981</t>
+          <t>-4.971948157141623</t>
         </is>
       </c>
       <c r="BC9" t="n">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4462,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>80.06</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-104.60</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4577,11 +4577,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.364746521969312</t>
+          <t>-6.526980741020981</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>2.19</v>
+        <v>3.58</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-11.30</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>94.57</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-9.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.01</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>80.06</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.39</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10.28404023044595</t>
+          <t>-8.364746521969312</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>9.24</v>
+        <v>2.19</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.24</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-18.53</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.57</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>71.34</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.40</t>
+          <t>-106.39</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1932.670103092784</t>
+          <t>1929.738421955403</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13.83303762581209</t>
+          <t>-10.28404023044595</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-7.71</v>
+        <v>9.24</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,22 +5840,22 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>656.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -5865,16 +5865,16 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>31.82121101204554</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-26.14</v>
+        <v>-4.36</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,22 +6271,22 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>792.6</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -6296,16 +6296,16 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>23.51</v>
+        <v>-26.14</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,22 +6702,22 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>867.2</t>
+          <t>792.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -6727,16 +6727,16 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-9.58</v>
+        <v>23.51</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,131 +7043,131 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>40.37</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>43.23</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>43.79</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-24.22</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-162.38</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>1663.117391304348</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>867.2</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>999.8</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-29.93</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-158.60</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>1663.301886792453</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>579.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>1050.4</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
+          <t>54.97412508298164</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>59.52</v>
+        <v>-9.58</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-154.22</t>
+          <t>-158.60</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,22 +7564,22 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1291.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1329.8</t>
+          <t>975.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1069.9</t>
+          <t>1050.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -7589,16 +7589,16 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>68.01783797577676</t>
+          <t>66.71115149108003</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>111.12</v>
+        <v>59.52</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>43.42</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-31.21</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-149.99</t>
+          <t>-154.22</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,22 +7995,22 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>1291.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1265.6</t>
+          <t>1329.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1069.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -8020,16 +8020,16 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>60.18138003141154</t>
+          <t>68.01783797577676</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>104.57</v>
+        <v>111.12</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>41.65</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-146.23</t>
+          <t>-149.99</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,17 +8426,17 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1615.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1421.2</t>
+          <t>1265.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -8456,11 +8456,11 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>52.1107552068259</t>
+          <t>60.18138003141154</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>155.66</v>
+        <v>104.57</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-14.52</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8529,17 +8529,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>42.57</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-25.52</t>
+          <t>-23.64</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-143.50</t>
+          <t>-146.23</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,17 +8857,17 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>1615.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1132.4</t>
+          <t>1421.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -8887,11 +8887,11 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>33.28385717187894</t>
+          <t>52.1107552068259</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>124.19</v>
+        <v>155.66</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,17 +9020,17 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-21.67</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.92999999999999</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.66</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-25.52</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-140.72</t>
+          <t>-143.50</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,17 +9288,17 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1125.2</t>
+          <t>1132.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -9318,11 +9318,11 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>16.75533859228556</t>
+          <t>33.28385717187894</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>172.73</v>
+        <v>124.19</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-14.52</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-20.72</t>
+          <t>-21.48</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,17 +9649,17 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9669,37 +9669,37 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.92999999999999</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-138.27</t>
+          <t>-140.72</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,17 +9719,17 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>970.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>810.0</t>
+          <t>1125.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -9749,11 +9749,11 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-11.60362420349809</t>
+          <t>16.75533859228556</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>59.22</v>
+        <v>172.73</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-20.72</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>43.06</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-136.46</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,29 +10150,29 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1663.301886792453</t>
+          <t>1663.117391304348</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1470.0</t>
+          <t>970.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
+          <t>810.0</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA23" t="inlineStr">
         <is>
           <t>0</t>
@@ -10180,11 +10180,11 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-24.48127731545686</t>
+          <t>-11.60362420349809</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>42.81</v>
+        <v>59.22</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-12.24</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1.98</v>
+        <v>-12.28</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-4.43</v>
+        <v>-1.98</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC4" t="n">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
+          <t>-3.962489301787693</t>
         </is>
       </c>
       <c r="BC6" t="n">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-103.19</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3.775715126621417</t>
+          <t>-3.87688447150315</t>
         </is>
       </c>
       <c r="BC7" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-27.35</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3.656151355397551</t>
+          <t>-3.775715126621417</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>3.58</v>
+        <v>-4.43</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-11.30</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-7.35</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4.971948157141623</t>
+          <t>-3.656151355397551</t>
         </is>
       </c>
       <c r="BC9" t="n">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>24.33</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>25.73</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.60</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6.526980741020981</t>
+          <t>-4.971948157141623</t>
         </is>
       </c>
       <c r="BC10" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>80.06</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-104.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.364746521969312</t>
+          <t>-6.526980741020981</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>2.19</v>
+        <v>3.58</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-11.30</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>94.57</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-9.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.01</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>80.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.39</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1929.738421955403</t>
+          <t>1926.441780821918</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10.28404023044595</t>
+          <t>-8.364746521969312</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>9.24</v>
+        <v>2.19</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>816</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,22 +5840,22 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>656.6</t>
+          <t>620.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -5865,16 +5865,16 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>21.40474887077532</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-4.36</v>
+        <v>-35.89</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,72 +6186,72 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,22 +6271,22 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>656.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -6296,16 +6296,16 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>31.82121101204554</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-26.14</v>
+        <v>-4.36</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,72 +6617,72 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,22 +6702,22 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>792.6</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -6727,16 +6727,16 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>23.51</v>
+        <v>-26.14</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>-1.9</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,72 +7048,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,22 +7133,22 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>867.2</t>
+          <t>792.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -7158,16 +7158,16 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-9.58</v>
+        <v>23.51</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7479,126 +7479,126 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>40.37</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>43.23</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>43.79</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-24.22</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-162.38</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>1661.576700434154</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>867.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>999.8</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-29.93</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-158.60</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>1663.117391304348</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>579.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>1050.4</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
+          <t>54.97412508298164</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>59.52</v>
+        <v>-9.58</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-154.22</t>
+          <t>-158.60</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,22 +7995,22 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1291.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1329.8</t>
+          <t>975.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1069.9</t>
+          <t>1050.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -8020,16 +8020,16 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>68.01783797577676</t>
+          <t>66.71115149108003</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>111.12</v>
+        <v>59.52</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>-1.9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>43.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-31.21</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-149.99</t>
+          <t>-154.22</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,22 +8426,22 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>1291.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1265.6</t>
+          <t>1329.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1069.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -8451,16 +8451,16 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>60.18138003141154</t>
+          <t>68.01783797577676</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>104.57</v>
+        <v>111.12</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>41.65</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-146.23</t>
+          <t>-149.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,17 +8857,17 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1615.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1421.2</t>
+          <t>1265.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -8887,11 +8887,11 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>52.1107552068259</t>
+          <t>60.18138003141154</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>155.66</v>
+        <v>104.57</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-14.52</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>42.57</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-25.52</t>
+          <t>-23.64</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-143.50</t>
+          <t>-146.23</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,17 +9288,17 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>1615.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1132.4</t>
+          <t>1421.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -9318,11 +9318,11 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>33.28385717187894</t>
+          <t>52.1107552068259</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>124.19</v>
+        <v>155.66</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-21.67</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.92999999999999</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.66</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-25.52</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-140.72</t>
+          <t>-143.50</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,17 +9719,17 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1125.2</t>
+          <t>1132.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -9749,11 +9749,11 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>16.75533859228556</t>
+          <t>33.28385717187894</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>172.73</v>
+        <v>124.19</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-14.52</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-20.72</t>
+          <t>-21.48</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,17 +10080,17 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10100,37 +10100,37 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.92999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-138.27</t>
+          <t>-140.72</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,17 +10150,17 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1663.117391304348</t>
+          <t>1661.576700434154</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>970.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>810.0</t>
+          <t>1125.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -10180,11 +10180,11 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-11.60362420349809</t>
+          <t>16.75533859228556</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>59.22</v>
+        <v>172.73</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -878,37 +878,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1034,52 +1034,52 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-12.28</v>
+        <v>-17.53</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1.98</v>
+        <v>-12.28</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-4.43</v>
+        <v>-1.98</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC6" t="n">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
+          <t>-3.962489301787693</t>
         </is>
       </c>
       <c r="BC7" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-103.19</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3.775715126621417</t>
+          <t>-3.87688447150315</t>
         </is>
       </c>
       <c r="BC8" t="n">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-27.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,11 +4146,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3.656151355397551</t>
+          <t>-3.775715126621417</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>3.58</v>
+        <v>-4.43</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-11.30</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-7.35</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4.971948157141623</t>
+          <t>-3.656151355397551</t>
         </is>
       </c>
       <c r="BC10" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>24.33</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
           <t>25.73</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.60</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6.526980741020981</t>
+          <t>-4.971948157141623</t>
         </is>
       </c>
       <c r="BC11" t="n">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>80.06</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-104.60</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1926.441780821918</t>
+          <t>1923.212820512821</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.364746521969312</t>
+          <t>-6.526980741020981</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>2.19</v>
+        <v>3.58</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-11.30</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>822</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5760,121 +5760,121 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>77.27</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>39.77</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>42.78</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>43.46</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-175.67</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>1660.072976878613</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>671.6</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>769.4</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-3.48</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-3.77</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>39.82</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>41.26</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>42.87</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-16.28</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-173.99</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>1661.576700434154</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>620.6</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>798.1</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>9.50704058356537</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-35.89</v>
+        <v>-55.93</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,22 +6271,22 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>656.6</t>
+          <t>620.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -6296,16 +6296,16 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>21.40474887077532</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-4.36</v>
+        <v>-35.89</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6374,17 +6374,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6622,67 +6622,67 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,22 +6702,22 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>656.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -6727,16 +6727,16 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>31.82121101204554</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-26.14</v>
+        <v>-4.36</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7053,67 +7053,67 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,22 +7133,22 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>792.6</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -7158,16 +7158,16 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>23.51</v>
+        <v>-26.14</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7484,67 +7484,67 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,22 +7564,22 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>867.2</t>
+          <t>792.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -7589,16 +7589,16 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-9.58</v>
+        <v>23.51</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7915,121 +7915,121 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>40.37</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>43.23</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>43.79</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-24.22</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-162.38</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>1660.072976878613</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>867.2</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>999.8</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-29.93</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-158.60</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>1661.576700434154</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>579.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>1050.4</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
+          <t>54.97412508298164</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>59.52</v>
+        <v>-9.58</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-154.22</t>
+          <t>-158.60</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,22 +8426,22 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1291.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1329.8</t>
+          <t>975.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1069.9</t>
+          <t>1050.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -8451,16 +8451,16 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>68.01783797577676</t>
+          <t>66.71115149108003</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>111.12</v>
+        <v>59.52</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>43.42</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-31.21</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-149.99</t>
+          <t>-154.22</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,22 +8857,22 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>1291.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1265.6</t>
+          <t>1329.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1069.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -8882,16 +8882,16 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>60.18138003141154</t>
+          <t>68.01783797577676</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>104.57</v>
+        <v>111.12</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>41.65</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-146.23</t>
+          <t>-149.99</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,17 +9288,17 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1615.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1421.2</t>
+          <t>1265.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -9318,11 +9318,11 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>52.1107552068259</t>
+          <t>60.18138003141154</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>155.66</v>
+        <v>104.57</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-14.52</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>42.57</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-25.52</t>
+          <t>-23.64</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-143.50</t>
+          <t>-146.23</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,17 +9719,17 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>1615.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1132.4</t>
+          <t>1421.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -9749,11 +9749,11 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>33.28385717187894</t>
+          <t>52.1107552068259</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>124.19</v>
+        <v>155.66</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-21.67</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.92999999999999</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.66</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-25.52</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-140.72</t>
+          <t>-143.50</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,17 +10150,17 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1661.576700434154</t>
+          <t>1660.072976878613</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1125.2</t>
+          <t>1132.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -10180,11 +10180,11 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>16.75533859228556</t>
+          <t>33.28385717187894</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>172.73</v>
+        <v>124.19</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-14.52</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI23"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,7 +913,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,42 +1019,42 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1059,27 +1064,27 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,12 +1104,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1129,168 +1134,173 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-17.53</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-8.836467204639346</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-18.96772606853415</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>49</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-7.59</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-9.26</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,39 +1319,39 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1455,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,7 +1465,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1465,52 +1475,52 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,12 +1540,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1560,168 +1570,173 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-12.28</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6.994420138476655</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-17.52925699846229</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>25</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-7.78</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1745,7 +1760,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,12 +1780,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1891,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,12 +1976,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1991,168 +2006,173 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-5.078995254842904</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-12.27682771984311</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>3</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>-7.78</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>17.54</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2176,7 +2196,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,12 +2216,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,12 +2412,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2422,168 +2442,173 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3.770298443024685</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-1.977756331821297</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>149</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-8.52</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-7.78</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>17.39</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2627,12 +2652,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2712,7 +2737,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2738,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,7 +2848,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2853,168 +2878,173 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4.09621519051621</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-4.433315868352679</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>-8.52</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>17.39</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>24.7</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3058,12 +3088,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,7 +3173,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3169,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,7 +3284,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3284,168 +3314,173 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4.034924158182307</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-4.433315868352679</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>-8.52</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>17.39</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>24.7</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3489,12 +3524,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3574,7 +3609,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3600,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,7 +3720,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3715,168 +3750,173 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3.962489301787693</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-4.433315868352679</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>-8.52</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>17.39</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>24.7</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,12 +3960,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,7 +4071,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-103.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4156,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,168 +4186,173 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3.775715126621417</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-4.43</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3.87688447150315</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-4.433315868352679</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>-8.52</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>17.39</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>24.7</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,39 +4371,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-27.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4592,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4577,150 +4622,150 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3.656151355397551</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3.775715126621417</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-4.433315868352679</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>97</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-11.30</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-8.52</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4730,15 +4775,20 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4782,12 +4832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4867,7 +4917,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4893,7 +4943,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-7.35</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,7 +5028,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -5008,168 +5058,173 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4.971948157141623</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3.656151355397551</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>3.580731054194842</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>-11.30</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>16.87</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,12 +5268,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,7 +5379,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>25.85</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>24.33</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
           <t>25.73</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.60</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5464,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1923.212820512821</t>
+          <t>1920.056313993174</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5439,168 +5494,173 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6.526980741020981</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4.971948157141623</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>3.580731054194842</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>-11.30</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>地心引力</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-79.67479674796748</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>6566.666666666667</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>3663.636363636364</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>16.87</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>47.42%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-424.62%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>文創100.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>23.9</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5619,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5649,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5729,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5755,7 +5815,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5825,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,22 +5900,22 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>545.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -5865,147 +5925,147 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>-55.93</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-0.2537794422296447</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-53.93828958410222</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>609</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
+      <c r="BH13" t="inlineStr">
         <is>
           <t>-17.01</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
+      <c r="BI13" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BK13" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BL13" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="BM13" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM13" t="inlineStr">
+      <c r="BN13" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ13" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BS13" t="inlineStr">
         <is>
           <t>3.22</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
+      <c r="BT13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BU13" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
+      <c r="BV13" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV13" t="inlineStr">
+      <c r="BW13" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY13" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ13" t="inlineStr">
+      <c r="CA13" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CB13" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CC13" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
       <c r="CD13" t="inlineStr">
         <is>
           <t>40.05</t>
@@ -6013,7 +6073,7 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6023,15 +6083,20 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CJ13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6050,7 +6115,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6065,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,7 +6225,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -6170,7 +6235,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,283 +6251,288 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>77.27</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>39.77</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>42.78</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>43.46</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-175.67</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>1658.995670995671</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>671.6</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>769.4</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-3.48</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-3.77</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>39.82</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>41.26</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>42.87</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-16.28</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-173.99</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>1660.072976878613</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>620.6</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>798.1</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>-35.89</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>9.50704058356537</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-55.93035499608936</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>414</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
+          <t>-17.01</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
+      <c r="BK14" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK14" t="inlineStr">
+      <c r="BL14" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL14" t="inlineStr">
+      <c r="BM14" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM14" t="inlineStr">
+      <c r="BN14" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="BO14" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO14" t="inlineStr">
+      <c r="BP14" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT14" t="inlineStr">
+      <c r="BU14" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU14" t="inlineStr">
+      <c r="BV14" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV14" t="inlineStr">
+      <c r="BW14" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY14" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ14" t="inlineStr">
+      <c r="CA14" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA14" t="inlineStr">
+      <c r="CB14" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB14" t="inlineStr">
+      <c r="CC14" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI14" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6481,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,7 +6687,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6697,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,22 +6772,22 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>656.6</t>
+          <t>620.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -6727,173 +6797,178 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>-4.36</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>21.40474887077532</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-35.8857929062109</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>399</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>-18.05</t>
-        </is>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="BK15" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK15" t="inlineStr">
+      <c r="BL15" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL15" t="inlineStr">
+      <c r="BM15" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM15" t="inlineStr">
+      <c r="BN15" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="BO15" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO15" t="inlineStr">
+      <c r="BP15" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP15" t="inlineStr">
+      <c r="BQ15" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT15" t="inlineStr">
+      <c r="BU15" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU15" t="inlineStr">
+      <c r="BV15" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV15" t="inlineStr">
+      <c r="BW15" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW15" t="inlineStr">
+      <c r="BX15" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY15" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ15" t="inlineStr">
+      <c r="CA15" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA15" t="inlineStr">
+      <c r="CB15" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB15" t="inlineStr">
+      <c r="CC15" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH15" t="inlineStr">
+      <c r="CI15" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI15" t="inlineStr">
+      <c r="CJ15" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6912,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,72 +7123,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,22 +7208,22 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>656.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -7158,173 +7233,178 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>-26.14</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>31.82121101204554</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-4.361925888305564</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>1024</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>-16.91</t>
-        </is>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
+          <t>-18.05</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="BK16" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK16" t="inlineStr">
+      <c r="BL16" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL16" t="inlineStr">
+      <c r="BM16" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM16" t="inlineStr">
+      <c r="BN16" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="BO16" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT16" t="inlineStr">
+      <c r="BU16" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU16" t="inlineStr">
+      <c r="BV16" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV16" t="inlineStr">
+      <c r="BW16" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW16" t="inlineStr">
+      <c r="BX16" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY16" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ16" t="inlineStr">
+      <c r="CA16" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA16" t="inlineStr">
+      <c r="CB16" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB16" t="inlineStr">
+      <c r="CC16" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH16" t="inlineStr">
+      <c r="CI16" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI16" t="inlineStr">
+      <c r="CJ16" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7348,7 +7428,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7479,72 +7559,72 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,22 +7644,22 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>792.6</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -7589,173 +7669,178 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>23.51</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>38.39996317574575</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-26.13633279528699</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>279</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>-16.70</t>
-        </is>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
+          <t>-16.91</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
+      <c r="BK17" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK17" t="inlineStr">
+      <c r="BL17" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL17" t="inlineStr">
+      <c r="BM17" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM17" t="inlineStr">
+      <c r="BN17" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="BO17" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO17" t="inlineStr">
+      <c r="BP17" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ17" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
       <c r="BS17" t="inlineStr">
         <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT17" t="inlineStr">
+      <c r="BU17" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU17" t="inlineStr">
+      <c r="BV17" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV17" t="inlineStr">
+      <c r="BW17" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW17" t="inlineStr">
+      <c r="BX17" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY17" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ17" t="inlineStr">
+      <c r="CA17" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA17" t="inlineStr">
+      <c r="CB17" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB17" t="inlineStr">
+      <c r="CC17" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>40.25</t>
-        </is>
-      </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH17" t="inlineStr">
+      <c r="CI17" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI17" t="inlineStr">
+      <c r="CJ17" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7774,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,72 +7995,72 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,22 +8080,22 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>867.2</t>
+          <t>792.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -8020,150 +8105,150 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>-9.58</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>50.13383517047897</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>23.51224065171425</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>1242</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>-16.49</t>
-        </is>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
+          <t>-16.70</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="BK18" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK18" t="inlineStr">
+      <c r="BL18" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL18" t="inlineStr">
+      <c r="BM18" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM18" t="inlineStr">
+      <c r="BN18" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="BO18" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr">
+      <c r="BP18" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT18" t="inlineStr">
+      <c r="BU18" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU18" t="inlineStr">
+      <c r="BV18" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV18" t="inlineStr">
+      <c r="BW18" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW18" t="inlineStr">
+      <c r="BX18" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY18" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ18" t="inlineStr">
+      <c r="CA18" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA18" t="inlineStr">
+      <c r="CB18" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB18" t="inlineStr">
+      <c r="CC18" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8173,20 +8258,25 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH18" t="inlineStr">
+      <c r="CI18" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI18" t="inlineStr">
+      <c r="CJ18" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8205,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8341,283 +8431,288 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>40.37</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>43.23</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>43.79</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-24.22</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-162.38</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>1658.995670995671</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>867.2</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>999.8</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-29.93</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-158.60</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>1660.072976878613</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>579.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>1050.4</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>54.97412508298164</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-9.579520161559458</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>159</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>-17.01</t>
-        </is>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
+          <t>-16.49</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
+      <c r="BK19" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK19" t="inlineStr">
+      <c r="BL19" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL19" t="inlineStr">
+      <c r="BM19" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM19" t="inlineStr">
+      <c r="BN19" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN19" t="inlineStr">
+      <c r="BO19" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO19" t="inlineStr">
+      <c r="BP19" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT19" t="inlineStr">
+      <c r="BU19" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU19" t="inlineStr">
+      <c r="BV19" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV19" t="inlineStr">
+      <c r="BW19" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW19" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY19" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ19" t="inlineStr">
+      <c r="CA19" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA19" t="inlineStr">
+      <c r="CB19" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB19" t="inlineStr">
+      <c r="CC19" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
+          <t>40.25</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH19" t="inlineStr">
+      <c r="CI19" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI19" t="inlineStr">
+      <c r="CJ19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8636,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,102 +8756,102 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-7.12</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-23.95</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
           <t>-0.37</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>24.29</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-03-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-03-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-02-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>-23.67</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>-1.24</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,7 +8867,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-154.22</t>
+          <t>-158.60</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,22 +8952,22 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1291.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1329.8</t>
+          <t>975.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1069.9</t>
+          <t>1050.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -8882,173 +8977,178 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>68.01783797577676</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>111.12</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>66.71115149108003</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>59.52437582524806</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>579</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>-16.70</t>
-        </is>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
+          <t>-17.01</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
+      <c r="BK20" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK20" t="inlineStr">
+      <c r="BL20" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL20" t="inlineStr">
+      <c r="BM20" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM20" t="inlineStr">
+      <c r="BN20" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN20" t="inlineStr">
+      <c r="BO20" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO20" t="inlineStr">
+      <c r="BP20" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT20" t="inlineStr">
+      <c r="BU20" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU20" t="inlineStr">
+      <c r="BV20" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV20" t="inlineStr">
+      <c r="BW20" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW20" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY20" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ20" t="inlineStr">
+      <c r="CA20" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA20" t="inlineStr">
+      <c r="CB20" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB20" t="inlineStr">
+      <c r="CC20" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC20" t="inlineStr">
+      <c r="CD20" t="inlineStr">
         <is>
           <t>40.15</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH20" t="inlineStr">
+      <c r="CI20" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI20" t="inlineStr">
+      <c r="CJ20" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9067,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,7 +9303,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>43.42</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-31.21</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-149.99</t>
+          <t>-154.22</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,22 +9388,22 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>1291.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1265.6</t>
+          <t>1329.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1069.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -9313,173 +9413,178 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>60.18138003141154</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>104.57</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>68.01783797577676</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>111.1183566697855</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>1291</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-16.49</t>
-        </is>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
+          <t>-16.70</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ21" t="inlineStr">
+      <c r="BK21" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK21" t="inlineStr">
+      <c r="BL21" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL21" t="inlineStr">
+      <c r="BM21" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM21" t="inlineStr">
+      <c r="BN21" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN21" t="inlineStr">
+      <c r="BO21" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO21" t="inlineStr">
+      <c r="BP21" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ21" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
       <c r="BS21" t="inlineStr">
         <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT21" t="inlineStr">
+      <c r="BU21" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU21" t="inlineStr">
+      <c r="BV21" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV21" t="inlineStr">
+      <c r="BW21" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW21" t="inlineStr">
+      <c r="BX21" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY21" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ21" t="inlineStr">
+      <c r="CA21" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA21" t="inlineStr">
+      <c r="CB21" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB21" t="inlineStr">
+      <c r="CC21" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC21" t="inlineStr">
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
         <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>41.65</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>40.25</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH21" t="inlineStr">
+      <c r="CI21" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI21" t="inlineStr">
+      <c r="CJ21" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9498,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,12 +9628,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9598,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,7 +9739,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-146.23</t>
+          <t>-149.99</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,17 +9824,17 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1615.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1421.2</t>
+          <t>1265.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -9749,168 +9854,173 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>52.1107552068259</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>155.66</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>60.18138003141154</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>104.5698165666325</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>692</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-14.52</t>
-        </is>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
+          <t>-16.49</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ22" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK22" t="inlineStr">
+      <c r="BL22" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL22" t="inlineStr">
+      <c r="BM22" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM22" t="inlineStr">
+      <c r="BN22" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN22" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO22" t="inlineStr">
+      <c r="BP22" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP22" t="inlineStr">
+      <c r="BQ22" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ22" t="inlineStr">
+      <c r="BR22" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT22" t="inlineStr">
+      <c r="BU22" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU22" t="inlineStr">
+      <c r="BV22" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV22" t="inlineStr">
+      <c r="BW22" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW22" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY22" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ22" t="inlineStr">
+      <c r="CA22" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA22" t="inlineStr">
+      <c r="CB22" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB22" t="inlineStr">
+      <c r="CC22" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>44.65</t>
-        </is>
-      </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
+          <t>40.25</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH22" t="inlineStr">
+      <c r="CI22" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI22" t="inlineStr">
+      <c r="CJ22" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9929,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9959,7 +10069,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10039,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,7 +10175,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>42.57</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-25.52</t>
+          <t>-23.64</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-143.50</t>
+          <t>-146.23</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,17 +10260,17 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1660.072976878613</t>
+          <t>1658.995670995671</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>1615.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1132.4</t>
+          <t>1421.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -10180,168 +10290,173 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>33.28385717187894</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>124.19</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>52.1107552068259</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>155.6586943990342</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>1615</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
           <t>48.2</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="BG23" t="inlineStr">
+      <c r="BH23" t="inlineStr">
         <is>
           <t>-14.52</t>
         </is>
       </c>
-      <c r="BH23" t="inlineStr">
+      <c r="BI23" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BJ23" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ23" t="inlineStr">
+      <c r="BK23" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK23" t="inlineStr">
+      <c r="BL23" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL23" t="inlineStr">
+      <c r="BM23" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="BM23" t="inlineStr">
+      <c r="BN23" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BN23" t="inlineStr">
+      <c r="BO23" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BO23" t="inlineStr">
+      <c r="BP23" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ23" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR23" t="inlineStr">
+      <c r="BS23" t="inlineStr">
         <is>
           <t>3.31</t>
         </is>
       </c>
-      <c r="BS23" t="inlineStr">
+      <c r="BT23" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="BT23" t="inlineStr">
+      <c r="BU23" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
+      <c r="BV23" t="inlineStr">
         <is>
           <t>47.06</t>
         </is>
       </c>
-      <c r="BV23" t="inlineStr">
+      <c r="BW23" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
+      <c r="BX23" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY23" t="inlineStr">
         <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="BZ23" t="inlineStr">
+      <c r="CA23" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA23" t="inlineStr">
+      <c r="CB23" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB23" t="inlineStr">
+      <c r="CC23" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>41.35</t>
-        </is>
-      </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>41.2</t>
         </is>
       </c>
-      <c r="CG23" t="inlineStr">
+      <c r="CH23" t="inlineStr">
         <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CH23" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CI23" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.94</t>
+          <t>-28.97</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,29 +1104,29 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>55.8</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1134,16 +1134,16 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-8.836467204639346</t>
+          <t>-10.43092782944423</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-18.96772606853415</t>
+          <t>-19.2004612658711</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1460,37 +1460,37 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1570,16 +1570,16 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
+          <t>-8.836467204639346</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-17.52925699846229</t>
+          <t>-18.96772606853415</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1911,52 +1911,52 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -2006,16 +2006,16 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-12.27682771984311</t>
+          <t>-17.52925699846229</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2442,16 +2442,16 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1.977756331821297</t>
+          <t>-12.27682771984311</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,17 +2580,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2768,67 +2768,67 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2878,16 +2878,16 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4.433315868352679</t>
+          <t>-1.977756331821297</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3204,67 +3204,67 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3640,67 +3640,67 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4076,67 +4076,67 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
+          <t>-3.962489301787693</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-103.19</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3.775715126621417</t>
+          <t>-3.87688447150315</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-27.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4948,67 +4948,67 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3.656151355397551</t>
+          <t>-3.775715126621417</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3.580731054194842</t>
+          <t>-4.433315868352679</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.30</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-7.35</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>33.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-103.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1920.056313993174</t>
+          <t>1916.920783645656</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4.971948157141623</t>
+          <t>-3.656151355397551</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>796</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5679,42 +5679,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-11.71</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,37 +5815,37 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>78.79</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -5855,32 +5855,32 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,32 +5890,32 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-175.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>561.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>635.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -5925,21 +5925,21 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-10.96402669051872</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-69.87038655610866</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>609</v>
+        <v>360</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6261,62 +6261,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,32 +6326,32 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>545.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -6361,21 +6361,21 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>-0.2537794422296447</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-53.93828958410222</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>414</v>
+        <v>609</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,131 +6687,131 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>77.27</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>39.77</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>42.78</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>43.46</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-175.67</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>1657.383285302594</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>671.6</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>769.4</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-3.48</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-3.77</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>39.82</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>41.26</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>42.87</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-16.28</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-173.99</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>1658.995670995671</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>620.6</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>798.1</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>9.50704058356537</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-35.8857929062109</t>
+          <t>-55.93035499608936</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7133,62 +7133,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,32 +7198,32 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>656.6</t>
+          <t>620.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -7233,21 +7233,21 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>21.40474887077532</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-4.361925888305564</t>
+          <t>-35.8857929062109</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>1024</v>
+        <v>399</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,72 +7559,72 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,32 +7634,32 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>656.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -7669,21 +7669,21 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>31.82121101204554</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-26.13633279528699</t>
+          <t>-4.361925888305564</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>279</v>
+        <v>1024</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,17 +7747,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,72 +7995,72 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,32 +8070,32 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>792.6</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -8105,21 +8105,21 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>23.51224065171425</t>
+          <t>-26.13633279528699</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1242</v>
+        <v>279</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,72 +8431,72 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,32 +8506,32 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>867.2</t>
+          <t>792.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -8541,21 +8541,21 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-9.579520161559458</t>
+          <t>23.51224065171425</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>159</v>
+        <v>1242</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,17 +8619,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,131 +8867,131 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>40.37</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>43.23</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>43.79</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-24.22</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-162.38</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>1657.383285302594</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>867.2</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>999.8</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-29.93</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-158.60</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>1658.995670995671</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>579.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>1050.4</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
+          <t>54.97412508298164</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>59.52437582524806</t>
+          <t>-9.579520161559458</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>579</v>
+        <v>159</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,102 +9192,102 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-7.12</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-23.95</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
           <t>-0.37</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>24.29</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-03-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-03-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-02-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-23.67</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>-1.24</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,32 +9378,32 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-154.22</t>
+          <t>-158.60</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1291.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1329.8</t>
+          <t>975.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1069.9</t>
+          <t>1050.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -9413,21 +9413,21 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>68.01783797577676</t>
+          <t>66.71115149108003</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>111.1183566697855</t>
+          <t>59.52437582524806</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>1291</v>
+        <v>579</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>43.42</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-31.21</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,32 +9814,32 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-149.99</t>
+          <t>-154.22</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>1291.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1265.6</t>
+          <t>1329.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1069.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -9849,21 +9849,21 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>60.18138003141154</t>
+          <t>68.01783797577676</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>104.5698165666325</t>
+          <t>111.1183566697855</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>692</v>
+        <v>1291</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>41.65</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-21.67</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,27 +10250,27 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-146.23</t>
+          <t>-149.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1658.995670995671</t>
+          <t>1657.383285302594</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1615.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1421.2</t>
+          <t>1265.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -10290,16 +10290,16 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>52.1107552068259</t>
+          <t>60.18138003141154</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>155.6586943990342</t>
+          <t>104.5698165666325</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>1615</v>
+        <v>692</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-14.52</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.97</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,114 +1019,114 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-7.73</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>24.57</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>24.62</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>24.84</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>26.92</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>11.29</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-101.37</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>1913.72193877551</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-7.72</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>24.68</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>26.98</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>19.98</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>11.29</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-101.40</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1916.920783645656</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1134,16 +1134,16 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10.43092782944423</t>
+          <t>-12.06591806681592</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-19.2004612658711</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,102 +1344,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>28.7</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-28.97</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10.61</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-1.45</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-07-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-07-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>28.7</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-27.94</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>10.61</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,29 +1540,29 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>55.8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1570,16 +1570,16 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-8.836467204639346</t>
+          <t>-10.43092782944423</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-18.96772606853415</t>
+          <t>-19.2004612658711</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,42 +1891,42 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1936,27 +1936,27 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -2006,16 +2006,16 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
+          <t>-8.836467204639346</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-17.52925699846229</t>
+          <t>-18.96772606853415</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -2347,52 +2347,52 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2442,16 +2442,16 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-12.27682771984311</t>
+          <t>-17.52925699846229</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2878,16 +2878,16 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1.977756331821297</t>
+          <t>-12.27682771984311</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-4.433315868352679</t>
+          <t>-1.977756331821297</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4071,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
+          <t>-3.962489301787693</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-103.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3.775715126621417</t>
+          <t>-3.87688447150315</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.56</t>
+          <t>-27.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.80</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1916.920783645656</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5494,16 +5494,16 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3.656151355397551</t>
+          <t>-3.775715126621417</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3.580731054194842</t>
+          <t>-4.433315868352679</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.30</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>802</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-11.71</t>
+          <t>-19.04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-23.38</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,72 +5815,72 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>78.79</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>39.89999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>40.72</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-175.86</t>
+          <t>-174.37</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>561.2</t>
+          <t>446.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>635.6</t>
+          <t>551.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -5925,21 +5925,21 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-105</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-10.96402669051872</t>
+          <t>-20.42357562622512</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-69.87038655610866</t>
+          <t>-72.4510947726103</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>360</v>
+        <v>451</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,42 +6115,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-11.71</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,37 +6251,37 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>78.79</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -6291,32 +6291,32 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-175.86</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,22 +6336,22 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>561.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>635.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -6361,21 +6361,21 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-10.96402669051872</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-69.87038655610866</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>609</v>
+        <v>360</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6697,62 +6697,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,22 +6772,22 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>545.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -6797,21 +6797,21 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>-0.2537794422296447</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-53.93828958410222</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>414</v>
+        <v>609</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,17 +6940,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,131 +7123,131 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>77.27</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>39.77</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>42.78</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>43.46</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-175.67</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>1655.971942446043</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>671.6</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>769.4</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-3.48</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-3.77</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>39.82</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>41.26</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>42.87</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-16.28</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-173.99</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>1657.383285302594</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>620.6</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>798.1</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>9.50704058356537</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-35.8857929062109</t>
+          <t>-55.93035499608936</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,62 +7569,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>656.6</t>
+          <t>620.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -7669,21 +7669,21 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>21.40474887077532</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-4.361925888305564</t>
+          <t>-35.8857929062109</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>1024</v>
+        <v>399</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,72 +7995,72 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,22 +8080,22 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>656.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -8105,21 +8105,21 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>31.82121101204554</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-26.13633279528699</t>
+          <t>-4.361925888305564</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>279</v>
+        <v>1024</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,72 +8431,72 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,22 +8516,22 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>792.6</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -8541,21 +8541,21 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>23.51224065171425</t>
+          <t>-26.13633279528699</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>1242</v>
+        <v>279</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,72 +8867,72 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,22 +8952,22 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>867.2</t>
+          <t>792.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -8977,21 +8977,21 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-9.579520161559458</t>
+          <t>23.51224065171425</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>159</v>
+        <v>1242</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,131 +9303,131 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>40.37</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>43.23</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>43.79</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-24.22</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-162.38</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>1655.971942446043</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>867.2</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>999.8</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-29.93</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-158.60</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>1657.383285302594</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>579.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>1050.4</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
+          <t>54.97412508298164</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>59.52437582524806</t>
+          <t>-9.579520161559458</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>579</v>
+        <v>159</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-154.22</t>
+          <t>-158.60</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,22 +9824,22 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1291.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1329.8</t>
+          <t>975.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1069.9</t>
+          <t>1050.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -9849,21 +9849,21 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>68.01783797577676</t>
+          <t>66.71115149108003</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>111.1183566697855</t>
+          <t>59.52437582524806</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>1291</v>
+        <v>579</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>43.42</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-31.21</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-149.99</t>
+          <t>-154.22</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,22 +10260,22 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1657.383285302594</t>
+          <t>1655.971942446043</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>1291.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1265.6</t>
+          <t>1329.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1069.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -10285,21 +10285,21 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>60.18138003141154</t>
+          <t>68.01783797577676</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>104.5698165666325</t>
+          <t>111.1183566697855</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>692</v>
+        <v>1291</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>40.15</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>41.65</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12.06591806681592</t>
+          <t>-13.44937134459196</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.97</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,119 +1450,119 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>-7.73</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>24.57</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>24.62</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>24.84</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>26.92</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>11.29</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-101.37</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1913.72193877551</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-7.72</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>24.68</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>26.98</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>19.98</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>11.29</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-101.40</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1913.72193877551</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1570,16 +1570,16 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.43092782944423</t>
+          <t>-12.06591806681592</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-19.2004612658711</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.94</t>
+          <t>-28.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1981,24 +1981,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>55.8</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA4" t="inlineStr">
         <is>
           <t>0</t>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8.836467204639346</t>
+          <t>-10.43092782944423</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-18.96772606853415</t>
+          <t>-19.2004612658711</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,47 +2322,47 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2372,27 +2372,27 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2442,16 +2442,16 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
+          <t>-8.836467204639346</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-17.52925699846229</t>
+          <t>-18.96772606853415</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,39 +2627,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -2783,52 +2783,52 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2878,16 +2878,16 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-12.27682771984311</t>
+          <t>-17.52925699846229</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1.977756331821297</t>
+          <t>-12.27682771984311</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-4.433315868352679</t>
+          <t>-1.977756331821297</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.39</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
+          <t>-3.962489301787693</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-103.19</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3.775715126621417</t>
+          <t>-3.87688447150315</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.38</t>
+          <t>-22.43</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5825,62 +5825,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.89999999999999</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-174.37</t>
+          <t>-171.42</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>446.6</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>551.6</t>
+          <t>592.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -5925,21 +5925,21 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-105</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-20.42357562622512</t>
+          <t>-22.19630447678222</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-72.4510947726103</t>
+          <t>-31.94631315484628</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>451</v>
+        <v>991</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-15.35</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-11.71</t>
+          <t>-19.04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-23.38</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,72 +6251,72 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>78.79</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>39.89999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>40.72</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-175.86</t>
+          <t>-174.37</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,22 +6336,22 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>561.2</t>
+          <t>446.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>635.6</t>
+          <t>551.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -6361,21 +6361,21 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-105</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-10.96402669051872</t>
+          <t>-20.42357562622512</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-69.87038655610866</t>
+          <t>-72.4510947726103</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>360</v>
+        <v>451</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,42 +6551,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-11.71</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,37 +6687,37 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>78.79</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -6727,32 +6727,32 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-175.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,22 +6772,22 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>561.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>635.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -6797,21 +6797,21 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-10.96402669051872</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-69.87038655610866</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>609</v>
+        <v>360</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7133,62 +7133,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,22 +7208,22 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>545.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -7233,21 +7233,21 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>-0.2537794422296447</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-53.93828958410222</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>414</v>
+        <v>609</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,17 +7376,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,131 +7559,131 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>77.27</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>39.77</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>42.78</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>43.46</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-175.67</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>1655.728448275862</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>671.6</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>769.4</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-3.48</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-3.77</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>39.82</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>41.26</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>42.87</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-16.28</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-173.99</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>1655.971942446043</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>620.6</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>798.1</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>9.50704058356537</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-35.8857929062109</t>
+          <t>-55.93035499608936</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,22 +8080,22 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>656.6</t>
+          <t>620.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -8105,21 +8105,21 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>21.40474887077532</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-4.361925888305564</t>
+          <t>-35.8857929062109</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1024</v>
+        <v>399</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8188,17 +8188,17 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,72 +8431,72 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,22 +8516,22 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>656.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -8541,21 +8541,21 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>31.82121101204554</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-26.13633279528699</t>
+          <t>-4.361925888305564</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>279</v>
+        <v>1024</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,72 +8867,72 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,22 +8952,22 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>792.6</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -8977,21 +8977,21 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>23.51224065171425</t>
+          <t>-26.13633279528699</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>1242</v>
+        <v>279</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,72 +9303,72 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,22 +9388,22 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>867.2</t>
+          <t>792.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -9413,21 +9413,21 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-9.579520161559458</t>
+          <t>23.51224065171425</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>159</v>
+        <v>1242</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,131 +9739,131 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>40.37</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>43.23</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>43.79</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-24.22</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-162.38</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>1655.728448275862</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>867.2</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>999.8</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-29.93</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-158.60</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>1655.971942446043</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>579.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>1050.4</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
+          <t>54.97412508298164</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>59.52437582524806</t>
+          <t>-9.579520161559458</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>579</v>
+        <v>159</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-31.21</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-154.22</t>
+          <t>-158.60</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,22 +10260,22 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1655.971942446043</t>
+          <t>1655.728448275862</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1291.0</t>
+          <t>579.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1329.8</t>
+          <t>975.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1069.9</t>
+          <t>1050.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -10285,21 +10285,21 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>68.01783797577676</t>
+          <t>66.71115149108003</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>111.1183566697855</t>
+          <t>59.52437582524806</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>1291</v>
+        <v>579</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>24.46</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>24.78</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>24.81</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>24.81</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>0</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-21.05836437236019</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>0</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>24.57</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>24.62</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>24.84</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>24.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>24.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>30.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-21.05836437236019</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>24</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>24.68</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>24.9</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>53.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>55.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-19.2004612658711</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>53</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>24.79</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>24.48</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>25.02</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>49.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>0</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-18.96772606853415</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>49</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>24.83</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>24.48</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>25.08</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>25.08</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>0</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-17.52925699846229</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>25</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>24.78</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>25.11</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>25.11</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>0</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-12.27682771984311</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>24.74</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>25.14</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>25.14</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>149.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>0</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1.977756331821297</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>149</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>24.7</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>24.39</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25.19</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>0</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-4.433315868352679</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>0</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>24.55</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>24.43</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>25.25</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>0</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-4.433315868352679</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>0</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>24.4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>24.36</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>25.32</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>0</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-4.433315868352679</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>0</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>24.25</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>25.41</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>25.41</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>0</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-4.433315868352679</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>0</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>40.23</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>40.64</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>42.46</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>42.46</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>991.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>565.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>565</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>592.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-31.94631315484628</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>991</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>991.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>39.89999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>40.72</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>451.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>446.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>446.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>551.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-72.4510947726103</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>451</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>451.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>39.73999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>40.83</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>42.6</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>360.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>561.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>561.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>635.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-69.87038655610866</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>360</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>39.73999999999999</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>40.96</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>42.69</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>42.69</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>609.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>545.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>545</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>668.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-53.93828958410222</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>609</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>609.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>39.77</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>42.78</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>42.78</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>414.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>671.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>671.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>769.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-55.93035499608936</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>414</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>39.82</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>41.26</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>42.87</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>42.87</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>399.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>620.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>620.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>798.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-35.8857929062109</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>399</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>399.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>39.98999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>42.97</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>42.97</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1024.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>656.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>656.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>993.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-4.361925888305564</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1024</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>40.12</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.64</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>43.07</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>43.07</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>279.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>710.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>710</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>987.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-26.13633279528699</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>279</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>40.16</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.78</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>43.15</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1242.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>792.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>792.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1106.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>23.51224065171425</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1242</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1242.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>40.37</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>41.92</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>43.23</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>43.23</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>867.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>867.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>999.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-9.579520161559458</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>159</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>40.56</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>43.32</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>579.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>975.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>975.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1050.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>59.52437582524806</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>579</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>579.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1029,48 +1029,48 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.78</v>
+        <v>24.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.81</v>
+        <v>24.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13.44937134459196</t>
+          <t>-14.6199856565563</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1459,53 +1459,53 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>24.62</v>
+        <v>24.78</v>
       </c>
       <c r="AN3" t="n">
-        <v>24.84</v>
+        <v>24.81</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1535,11 +1535,11 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12.06591806681592</t>
+          <t>-13.44937134459196</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.97</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.53</v>
+        <v>24.62</v>
       </c>
       <c r="AN4" t="n">
-        <v>24.9</v>
+        <v>24.84</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1965,11 +1965,11 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>55.8</v>
+        <v>30.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-10.43092782944423</t>
+          <t>-12.06591806681592</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-19.2004612658711</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.94</t>
+          <t>-28.97</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.48</v>
+        <v>24.53</v>
       </c>
       <c r="AN5" t="n">
-        <v>25.02</v>
+        <v>24.9</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2395,11 +2395,11 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>55.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8.836467204639346</t>
+          <t>-10.43092782944423</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-18.96772606853415</t>
+          <t>-19.2004612658711</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM6" t="n">
         <v>24.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>25.08</v>
+        <v>25.02</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
+          <t>-8.836467204639346</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-17.52925699846229</t>
+          <t>-18.96772606853415</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,39 +3033,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -3189,48 +3189,48 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>24.45</v>
+        <v>24.48</v>
       </c>
       <c r="AN7" t="n">
-        <v>25.11</v>
+        <v>25.08</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-12.27682771984311</t>
+          <t>-17.52925699846229</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>24.42</v>
+        <v>24.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.14</v>
+        <v>25.11</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1.977756331821297</t>
+          <t>-12.27682771984311</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>24.39</v>
+        <v>24.42</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.19</v>
+        <v>25.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-4.433315868352679</t>
+          <t>-1.977756331821297</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4464,63 +4464,63 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>24.43</v>
+        <v>24.39</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.25</v>
+        <v>25.19</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4586,17 +4586,17 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4894,63 +4894,63 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>24.36</v>
+        <v>24.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.32</v>
+        <v>25.25</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>24.32</v>
+        <v>24.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.41</v>
+        <v>25.32</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.19</t>
+          <t>-102.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3.87688447150315</t>
+          <t>-3.962489301787693</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5446,17 +5446,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.64</v>
+        <v>40.57</v>
       </c>
       <c r="AN13" t="n">
-        <v>42.46</v>
+        <v>42.39</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>16.52</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-171.42</t>
+          <t>-167.48</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>592.8</t>
+          <t>638.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-22.19630447678222</t>
+          <t>-23.50368966397576</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-31.94631315484628</t>
+          <t>-30.69430819354022</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-15.35</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.38</t>
+          <t>-22.43</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.89999999999999</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.72</v>
+        <v>40.64</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.52</v>
+        <v>42.46</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-174.37</t>
+          <t>-171.42</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>446.6</v>
+        <v>565</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>551.6</t>
+          <t>592.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-105</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-20.42357562622512</t>
+          <t>-22.19630447678222</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-72.4510947726103</t>
+          <t>-31.94631315484628</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-15.35</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-11.71</t>
+          <t>-19.04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-23.38</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>78.79</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>39.89999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>40.83</v>
+        <v>40.72</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.6</v>
+        <v>42.52</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-175.86</t>
+          <t>-174.37</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,20 +6690,20 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>561.2</v>
+        <v>446.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>635.6</t>
+          <t>551.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-105</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-10.96402669051872</t>
+          <t>-20.42357562622512</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-69.87038655610866</t>
+          <t>-72.4510947726103</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,42 +6903,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-11.71</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,37 +7039,37 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>78.79</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -7078,29 +7078,29 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.96</v>
+        <v>40.83</v>
       </c>
       <c r="AN16" t="n">
-        <v>42.69</v>
+        <v>42.6</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-175.86</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,20 +7120,20 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>545</v>
+        <v>561.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>635.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
@@ -7141,22 +7141,22 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-10.96402669051872</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-69.87038655610866</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,58 +7479,58 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>41.1</v>
+        <v>40.96</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.78</v>
+        <v>42.69</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,20 +7550,20 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>671.6</v>
+        <v>545</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
@@ -7571,22 +7571,22 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>-0.2537794422296447</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-53.93828958410222</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>41.26</v>
+        <v>41.1</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.87</v>
+        <v>42.78</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-16.28</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-173.99</t>
+          <t>-175.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,20 +7980,20 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>620.6</v>
+        <v>671.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>798.1</t>
+          <t>769.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>9.50704058356537</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-35.8857929062109</t>
+          <t>-55.93035499608936</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>41.45</v>
+        <v>41.26</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.97</v>
+        <v>42.87</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,20 +8410,20 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>656.6</v>
+        <v>620.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
@@ -8431,22 +8431,22 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>21.40474887077532</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-4.361925888305564</t>
+          <t>-35.8857929062109</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>41.64</v>
+        <v>41.45</v>
       </c>
       <c r="AN20" t="n">
-        <v>43.07</v>
+        <v>42.97</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,20 +8840,20 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>710</v>
+        <v>656.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
@@ -8861,22 +8861,22 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>31.82121101204554</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-26.13633279528699</t>
+          <t>-4.361925888305564</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>41.78</v>
+        <v>41.64</v>
       </c>
       <c r="AN21" t="n">
-        <v>43.15</v>
+        <v>43.07</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,20 +9270,20 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>792.6</v>
+        <v>710</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
@@ -9291,22 +9291,22 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>23.51224065171425</t>
+          <t>-26.13633279528699</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.92</v>
+        <v>41.78</v>
       </c>
       <c r="AN22" t="n">
-        <v>43.23</v>
+        <v>43.15</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,20 +9700,20 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>867.2</v>
+        <v>792.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-9.579520161559458</t>
+          <t>23.51224065171425</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.48</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.37</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>42.06</v>
+        <v>41.92</v>
       </c>
       <c r="AN23" t="n">
-        <v>43.32</v>
+        <v>43.23</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-24.22</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-158.60</t>
+          <t>-162.38</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,20 +10130,20 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1655.728448275862</t>
+          <t>1654.685078909612</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>975.6</v>
+        <v>867.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1050.4</t>
+          <t>999.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
@@ -10151,22 +10151,22 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-132</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>66.71115149108003</t>
+          <t>54.97412508298164</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>59.52437582524806</t>
+          <t>-9.579520161559458</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>579.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.49</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -908,14 +908,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>0</t>
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1034,43 +1034,43 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.82</v>
+        <v>24.88</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.8</v>
+        <v>24.77</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-14.6199856565563</t>
+          <t>-15.61050545898767</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1338,14 +1338,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1459,48 +1459,48 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>24.78</v>
+        <v>24.82</v>
       </c>
       <c r="AN3" t="n">
-        <v>24.81</v>
+        <v>24.8</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13.44937134459196</t>
+          <t>-14.6199856565563</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,14 +1768,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1889,53 +1889,53 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.62</v>
+        <v>24.78</v>
       </c>
       <c r="AN4" t="n">
-        <v>24.84</v>
+        <v>24.81</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1965,11 +1965,11 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12.06591806681592</t>
+          <t>-13.44937134459196</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.97</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.53</v>
+        <v>24.62</v>
       </c>
       <c r="AN5" t="n">
-        <v>24.9</v>
+        <v>24.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2395,11 +2395,11 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>55.8</v>
+        <v>30.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10.43092782944423</t>
+          <t>-12.06591806681592</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-19.2004612658711</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.94</t>
+          <t>-28.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>24.48</v>
+        <v>24.53</v>
       </c>
       <c r="AN6" t="n">
-        <v>25.02</v>
+        <v>24.9</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2825,11 +2825,11 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>55.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8.836467204639346</t>
+          <t>-10.43092782944423</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-18.96772606853415</t>
+          <t>-19.2004612658711</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3174,63 +3174,63 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM7" t="n">
         <v>24.48</v>
       </c>
       <c r="AN7" t="n">
-        <v>25.08</v>
+        <v>25.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
+          <t>-8.836467204639346</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-17.52925699846229</t>
+          <t>-18.96772606853415</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,39 +3463,39 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.89</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -3619,48 +3619,48 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>24.45</v>
+        <v>24.48</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.11</v>
+        <v>25.08</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-12.27682771984311</t>
+          <t>-17.52925699846229</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>24.42</v>
+        <v>24.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.14</v>
+        <v>25.11</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1.977756331821297</t>
+          <t>-12.27682771984311</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.35</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4464,63 +4464,63 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>24.39</v>
+        <v>24.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.19</v>
+        <v>25.14</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4.09621519051621</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-4.433315868352679</t>
+          <t>-1.977756331821297</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4894,63 +4894,63 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>24.43</v>
+        <v>24.39</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.25</v>
+        <v>25.19</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.64</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4.034924158182307</t>
+          <t>-4.09621519051621</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>24.36</v>
+        <v>24.43</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.32</v>
+        <v>25.25</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.90</t>
+          <t>-102.64</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3.962489301787693</t>
+          <t>-4.034924158182307</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.57</v>
+        <v>40.53</v>
       </c>
       <c r="AN13" t="n">
-        <v>42.39</v>
+        <v>42.34</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>33.89</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-167.48</t>
+          <t>-162.21</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>606</v>
+        <v>658.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>638.8</t>
+          <t>601.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>56</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-23.50368966397576</t>
+          <t>-21.46089848733141</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-30.69430819354022</t>
+          <t>-10.22554701578747</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>41.0</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.64</v>
+        <v>40.57</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.46</v>
+        <v>42.39</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>16.52</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-171.42</t>
+          <t>-167.48</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>592.8</t>
+          <t>638.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-22.19630447678222</t>
+          <t>-23.50368966397576</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-31.94631315484628</t>
+          <t>-30.69430819354022</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-15.35</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.38</t>
+          <t>-22.43</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.89999999999999</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>40.72</v>
+        <v>40.64</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.52</v>
+        <v>42.46</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-174.37</t>
+          <t>-171.42</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,20 +6690,20 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>446.6</v>
+        <v>565</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>551.6</t>
+          <t>592.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-105</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-20.42357562622512</t>
+          <t>-22.19630447678222</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-72.4510947726103</t>
+          <t>-31.94631315484628</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-15.35</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-11.71</t>
+          <t>-19.04</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-23.38</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>78.79</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>39.89999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.83</v>
+        <v>40.72</v>
       </c>
       <c r="AN16" t="n">
-        <v>42.6</v>
+        <v>42.52</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-175.86</t>
+          <t>-174.37</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,20 +7120,20 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>561.2</v>
+        <v>446.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>635.6</t>
+          <t>551.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
@@ -7141,22 +7141,22 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-105</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-10.96402669051872</t>
+          <t>-20.42357562622512</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-69.87038655610866</t>
+          <t>-72.4510947726103</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,42 +7333,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-11.71</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,37 +7469,37 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>78.79</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -7508,29 +7508,29 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.96</v>
+        <v>40.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.69</v>
+        <v>42.6</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-175.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,20 +7550,20 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>545</v>
+        <v>561.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>635.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
@@ -7571,22 +7571,22 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-10.96402669051872</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-69.87038655610866</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>41.1</v>
+        <v>40.96</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.78</v>
+        <v>42.69</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,20 +7980,20 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>671.6</v>
+        <v>545</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>-0.2537794422296447</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-53.93828958410222</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>41.26</v>
+        <v>41.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.87</v>
+        <v>42.78</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-16.28</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-173.99</t>
+          <t>-175.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,20 +8410,20 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>620.6</v>
+        <v>671.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>798.1</t>
+          <t>769.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
@@ -8431,22 +8431,22 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>9.50704058356537</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-35.8857929062109</t>
+          <t>-55.93035499608936</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,58 +8769,58 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>41.45</v>
+        <v>41.26</v>
       </c>
       <c r="AN20" t="n">
-        <v>42.97</v>
+        <v>42.87</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,20 +8840,20 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>656.6</v>
+        <v>620.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
@@ -8861,22 +8861,22 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>21.40474887077532</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-4.361925888305564</t>
+          <t>-35.8857929062109</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>-33.89</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.98999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>41.64</v>
+        <v>41.45</v>
       </c>
       <c r="AN21" t="n">
-        <v>43.07</v>
+        <v>42.97</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-15.57</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-170.98</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,20 +9270,20 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>710</v>
+        <v>656.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>993.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
@@ -9291,22 +9291,22 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>-336</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>31.82121101204554</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-26.13633279528699</t>
+          <t>-4.361925888305564</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-28.12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.78</v>
+        <v>41.64</v>
       </c>
       <c r="AN22" t="n">
-        <v>43.15</v>
+        <v>43.07</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-165.57</t>
+          <t>-168.22</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,20 +9700,20 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>792.6</v>
+        <v>710</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1106.9</t>
+          <t>987.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-277</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>50.13383517047897</t>
+          <t>38.39996317574575</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>23.51224065171425</t>
+          <t>-26.13633279528699</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1242.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.48</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.92</v>
+        <v>41.78</v>
       </c>
       <c r="AN23" t="n">
-        <v>43.23</v>
+        <v>43.15</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-162.38</t>
+          <t>-165.57</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,20 +10130,20 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1654.685078909612</t>
+          <t>1654.184097421203</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>867.2</v>
+        <v>792.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>999.8</t>
+          <t>1106.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
@@ -10151,22 +10151,22 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-132</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>54.97412508298164</t>
+          <t>50.13383517047897</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-9.579520161559458</t>
+          <t>23.51224065171425</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>1242.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ13"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>3629</t>
@@ -894,24 +898,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>24.35</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>0</t>
@@ -924,37 +928,37 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -964,12 +968,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -979,17 +983,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -999,12 +1003,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -1020,83 +1024,83 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>24.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>24.72</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1122,12 +1126,12 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17.1578263337917</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1142,17 +1146,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1197,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1207,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1277,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1299,22 +1303,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,37 +1358,37 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1394,12 +1398,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1409,12 +1413,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1424,12 +1428,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,106 +1444,106 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>95.56</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>40.47</v>
+        <v>24.71</v>
       </c>
       <c r="AN3" t="n">
-        <v>42.28</v>
+        <v>24.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-156.65</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>677.8</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>619.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1547,22 +1551,22 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-22.2425718763521</t>
+          <t>-16.44863759950652</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-26.54177551596592</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1572,27 +1576,27 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -1607,27 +1611,27 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1637,52 +1641,52 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1692,32 +1696,32 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1729,22 +1733,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1754,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1764,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1774,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1784,37 +1788,37 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1824,12 +1828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1839,12 +1843,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1854,12 +1858,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1870,106 +1874,106 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>40.53</v>
+        <v>24.88</v>
       </c>
       <c r="AN4" t="n">
-        <v>42.34</v>
+        <v>24.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>33.89</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-162.21</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>658.2</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>601.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -1977,22 +1981,22 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-21.46089848733141</t>
+          <t>-15.61050545898767</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10.22554701578747</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2002,27 +2006,27 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -2037,82 +2041,82 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2122,32 +2126,32 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2159,22 +2163,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2184,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2194,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2204,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2214,37 +2218,37 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2254,12 +2258,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2269,12 +2273,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2284,12 +2288,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2300,106 +2304,106 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>40.57</v>
+        <v>24.82</v>
       </c>
       <c r="AN5" t="n">
-        <v>42.39</v>
+        <v>24.8</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-167.48</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>606</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>638.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2407,22 +2411,22 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-23.50368966397576</t>
+          <t>-14.6199856565563</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-30.69430819354022</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2432,27 +2436,27 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -2467,82 +2471,82 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2552,32 +2556,32 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2594,17 +2598,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2614,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2624,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2634,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2644,37 +2648,37 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2684,12 +2688,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -2699,12 +2703,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2714,12 +2718,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2730,106 +2734,106 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>40.64</v>
+        <v>24.78</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.46</v>
+        <v>24.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>16.52</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-171.42</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>592.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -2837,22 +2841,22 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-22.19630447678222</t>
+          <t>-13.44937134459196</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-31.94631315484628</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2862,27 +2866,27 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
@@ -2897,82 +2901,82 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -2982,32 +2986,32 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3024,17 +3028,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3044,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3054,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3064,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3074,37 +3078,37 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3114,12 +3118,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3129,12 +3133,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.38</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -3144,12 +3148,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3160,106 +3164,106 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.89999999999999</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>40.72</v>
+        <v>24.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.52</v>
+        <v>24.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-174.37</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>446.6</v>
+        <v>30.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>551.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3267,22 +3271,22 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-105</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-20.42357562622512</t>
+          <t>-12.06591806681592</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-72.4510947726103</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3292,27 +3296,27 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -3327,27 +3331,27 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3357,52 +3361,52 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3412,32 +3416,32 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3454,17 +3458,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3474,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3484,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3494,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3504,37 +3508,37 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3544,12 +3548,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3559,12 +3563,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-28.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -3574,12 +3578,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3590,106 +3594,106 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>78.79</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>40.83</v>
+        <v>24.53</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.6</v>
+        <v>24.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-175.86</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>561.2</v>
+        <v>55.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>635.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -3697,22 +3701,22 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10.96402669051872</t>
+          <t>-10.43092782944423</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-69.87038655610866</t>
+          <t>-19.2004612658711</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3722,27 +3726,27 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
@@ -3757,27 +3761,27 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3787,52 +3791,52 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -3842,32 +3846,32 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -3879,52 +3883,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-1.83</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3934,37 +3938,37 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3974,12 +3978,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -3989,12 +3993,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4004,12 +4008,12 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4020,106 +4024,106 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>40.96</v>
+        <v>24.48</v>
       </c>
       <c r="AN9" t="n">
-        <v>42.69</v>
+        <v>25.02</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
@@ -4127,22 +4131,22 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-8.836467204639346</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-18.96772606853415</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4152,27 +4156,27 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -4187,27 +4191,27 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4217,52 +4221,52 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4272,32 +4276,32 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4309,22 +4313,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4334,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4344,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4354,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4364,37 +4368,37 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4404,12 +4408,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4419,12 +4423,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -4434,12 +4438,12 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4450,106 +4454,106 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>41.1</v>
+        <v>24.48</v>
       </c>
       <c r="AN10" t="n">
-        <v>42.78</v>
+        <v>25.08</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>671.6</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -4557,22 +4561,22 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-17.52925699846229</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4582,27 +4586,27 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
@@ -4617,27 +4621,27 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4647,52 +4651,52 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4702,32 +4706,32 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -4739,22 +4743,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4764,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4774,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4784,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4794,37 +4798,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4834,12 +4838,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -4849,12 +4853,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -4864,12 +4868,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4880,106 +4884,106 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>41.26</v>
+        <v>24.45</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.87</v>
+        <v>25.11</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.28</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-173.99</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>620.6</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>798.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
@@ -4987,22 +4991,22 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-35.8857929062109</t>
+          <t>-12.27682771984311</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5012,27 +5016,27 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
@@ -5047,82 +5051,82 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5132,32 +5136,32 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5169,22 +5173,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5194,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5204,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5214,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5224,37 +5228,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-03-05 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-02-20 00:00:00</t>
+          <t>2024-07-02 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-03-04 00:00:00</t>
+          <t>2024-07-10 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5264,12 +5268,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5279,12 +5283,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -5294,12 +5298,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5310,106 +5314,106 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>51.32</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>41.45</v>
+        <v>24.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>42.97</v>
+        <v>25.14</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-102.14</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1913.72193877551</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>656.6</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
@@ -5417,22 +5421,22 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>-3.770298443024685</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-4.361925888305564</t>
+          <t>-1.977756331821297</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5442,27 +5446,27 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>誠品生活</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -5477,27 +5481,27 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>5.61175015634552</t>
+          <t>-79.67479674796748</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>2.720079552075342</t>
+          <t>6566.666666666667</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>2.597352307479901</t>
+          <t>3663.636363636364</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5507,52 +5511,52 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>38.48%</t>
+          <t>47.42%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-424.62%</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>799</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+          <t>文創100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>誠品生活-文化創意業-上櫃</t>
+          <t>地心引力-文化創意業-上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5562,32 +5566,32 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+          <t>** 文化創意業 - 數位內容產業、創意生活產業</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -5599,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5609,7 +5613,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5624,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5634,7 +5638,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -5644,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-28.12</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5709,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-22.81</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5719,7 +5723,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -5729,7 +5733,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5740,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>76.51</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>41.64</v>
+        <v>40.42</v>
       </c>
       <c r="AN13" t="n">
-        <v>43.07</v>
+        <v>42.2</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5816,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-168.22</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5826,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1652.800429184549</t>
+          <t>1651.024285714286</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>710</v>
+        <v>642.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>987.8</t>
+          <t>544.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5847,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-277</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>38.39996317574575</t>
+          <t>-26.69365175355818</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-26.13633279528699</t>
+          <t>-51.17459107819161</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5882,145 +5886,4445 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
+          <t>-15.77</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>40.6</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-0.72</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9.41</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-21.86</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>86.67</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>95.56</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-4.28</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>40.89</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>42.28</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>43.12</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-156.65</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>458.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>677.8</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>619.5</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-22.2425718763521</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-26.54177551596592</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>458.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>-14.73</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>41.1</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-1.97</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9.41</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-21.29</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15.33</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-4.27</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>40.68</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>43.16</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>33.89</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.72</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-162.21</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>870.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>658.2</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>601.6</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-21.46089848733141</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-10.22554701578747</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>870.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-14.11</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-5.13</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-22.34</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10.95</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-4.3</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>40.4</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-167.48</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>619.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>606</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>638.8</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-32</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-23.50368966397576</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-30.69430819354022</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>619.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>-15.25</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-4.69</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-22.43</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17.52</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>93.94</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-1.00</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-4.29</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>-1.83</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>40.23</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>16.52</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-171.42</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>991.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>565</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>592.8</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-27</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-22.19630447678222</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-31.94631315484628</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>991.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>-15.35</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-19.04</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-23.38</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-2.48</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>86.36</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-2.00</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>-1.78</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>39.89999999999999</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>43.3</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-174.37</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>451.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>446.6</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>551.6</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-105</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-20.42357562622512</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>-72.4510947726103</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>451.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>-16.39</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-11.71</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-23.86</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>81.82</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>78.79</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-4.16</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>39.73999999999999</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>43.35</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-175.86</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>561.2</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>635.6</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-74</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-10.96402669051872</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-69.87038655610866</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
           <t>-16.91</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BI19" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>誠品生活</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BK19" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="BL19" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM13" t="inlineStr">
+      <c r="BM19" t="inlineStr">
         <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BN19" t="inlineStr">
         <is>
           <t>5.61175015634552</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BO19" t="inlineStr">
         <is>
           <t>2.720079552075342</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BP19" t="inlineStr">
         <is>
           <t>2.597352307479901</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
+      <c r="BS19" t="inlineStr">
         <is>
           <t>3.22</t>
         </is>
       </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BT19" t="inlineStr">
         <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
+      <c r="BU19" t="inlineStr">
         <is>
           <t>36.81</t>
         </is>
       </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>48.35</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
         <is>
           <t>38.48%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>354.12</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
         <is>
           <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CB19" t="inlineStr">
         <is>
           <t>誠品生活-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
+      <c r="CC19" t="inlineStr">
         <is>
           <t>文化創意業右下上櫃</t>
         </is>
       </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
+      <c r="CD19" t="inlineStr">
         <is>
           <t>40.05</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>39.85</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
         <is>
           <t>40.05</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CH19" t="inlineStr">
         <is>
           <t>12.44</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CI19" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-18.51</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-23.95</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10.95</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>77.27</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>51.52</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-2.98</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-4.05</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>39.73999999999999</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>43.4</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-176.24</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>609.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>545</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>668.8</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-123</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-0.2537794422296447</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-53.93828958410222</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>609.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>-17.01</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-12.71</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-23.95</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>77.27</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>39.77</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>43.46</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-175.67</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>671.6</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>769.4</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-97</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>9.50704058356537</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-55.93035499608936</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>-17.01</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-22.24</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-25.57</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-3.48</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>39.82</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>43.53</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-16.28</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-1.00</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-173.99</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>399.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>620.6</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>798.1</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-177</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>21.40474887077532</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-35.8857929062109</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>399.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>39.35</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>38.75</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-33.89</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-24.90</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18.98</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-3.54</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>39.98999999999999</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>43.6</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-15.57</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-170.98</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>1651.024285714286</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>656.6</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>993.2</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-336</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>31.82121101204554</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-4.361925888305564</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>-18.05</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>47.76</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>360.23</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>39.85</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>** 貿易百貨 - 貿易商、代理商、經銷商、零售通路** 文化創意業 - 創意生活產業</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.56</v>
+        <v>24.46</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.72</v>
+        <v>24.71</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-17.1578263337917</t>
+          <t>-17.75790910895608</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1469,17 +1469,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,19 +1488,19 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>24.71</v>
+        <v>24.56</v>
       </c>
       <c r="AN3" t="n">
-        <v>24.74</v>
+        <v>24.72</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-16.44863759950652</t>
+          <t>-17.1578263337917</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1894,43 +1894,43 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.88</v>
+        <v>24.71</v>
       </c>
       <c r="AN4" t="n">
-        <v>24.77</v>
+        <v>24.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.35</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-15.61050545898767</t>
+          <t>-16.44863759950652</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2324,43 +2324,43 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.82</v>
+        <v>24.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>24.8</v>
+        <v>24.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-14.6199856565563</t>
+          <t>-15.61050545898767</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2749,48 +2749,48 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>24.78</v>
+        <v>24.82</v>
       </c>
       <c r="AN6" t="n">
-        <v>24.81</v>
+        <v>24.8</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13.44937134459196</t>
+          <t>-14.6199856565563</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3179,53 +3179,53 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>24.62</v>
+        <v>24.78</v>
       </c>
       <c r="AN7" t="n">
-        <v>24.84</v>
+        <v>24.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3255,11 +3255,11 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12.06591806681592</t>
+          <t>-13.44937134459196</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.97</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>24.53</v>
+        <v>24.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>24.9</v>
+        <v>24.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,11 +3685,11 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>55.8</v>
+        <v>30.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
@@ -3706,17 +3706,17 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10.43092782944423</t>
+          <t>-12.06591806681592</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-19.2004612658711</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.94</t>
+          <t>-28.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>24.48</v>
+        <v>24.53</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.02</v>
+        <v>24.9</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>55.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.836467204639346</t>
+          <t>-10.43092782944423</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-18.96772606853415</t>
+          <t>-19.2004612658711</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4464,63 +4464,63 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM10" t="n">
         <v>24.48</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.08</v>
+        <v>25.02</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
+          <t>-8.836467204639346</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-17.52925699846229</t>
+          <t>-18.96772606853415</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,39 +4753,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.89</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-2.68</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -4909,48 +4909,48 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>24.45</v>
+        <v>24.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.11</v>
+        <v>25.08</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-12.27682771984311</t>
+          <t>-17.52925699846229</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>24.42</v>
+        <v>24.45</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.14</v>
+        <v>25.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>53.14</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.14</t>
+          <t>-101.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3.770298443024685</t>
+          <t>-5.078995254842904</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1.977756331821297</t>
+          <t>-12.27682771984311</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.81</t>
+          <t>-22.05</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>76.51</t>
+          <t>66.98</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.42</v>
+        <v>40.4</v>
       </c>
       <c r="AN13" t="n">
-        <v>42.2</v>
+        <v>42.14</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>41.60</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-151.77</t>
+          <t>-146.89</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>494.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>642.2</v>
+        <v>542.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>544.4</t>
+          <t>553.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-26.69365175355818</t>
+          <t>-30.36588951374844</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-51.17459107819161</t>
+          <t>-50.56319719479484</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>494.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-15.77</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-22.81</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>95.56</t>
+          <t>76.51</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.47</v>
+        <v>40.42</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.28</v>
+        <v>42.2</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-156.65</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>677.8</v>
+        <v>642.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>619.5</t>
+          <t>544.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-22.2425718763521</t>
+          <t>-26.69365175355818</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-26.54177551596592</t>
+          <t>-51.17459107819161</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.77</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.56</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>40.53</v>
+        <v>40.47</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.34</v>
+        <v>42.28</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.12</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>33.89</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-162.21</t>
+          <t>-156.65</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,20 +6690,20 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>658.2</v>
+        <v>677.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>601.6</t>
+          <t>619.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-21.46089848733141</t>
+          <t>-22.2425718763521</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-10.22554701578747</t>
+          <t>-26.54177551596592</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.57</v>
+        <v>40.53</v>
       </c>
       <c r="AN16" t="n">
-        <v>42.39</v>
+        <v>42.34</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>33.89</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-167.48</t>
+          <t>-162.21</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,20 +7120,20 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>606</v>
+        <v>658.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>638.8</t>
+          <t>601.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
@@ -7141,22 +7141,22 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>56</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-23.50368966397576</t>
+          <t>-21.46089848733141</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-30.69430819354022</t>
+          <t>-10.22554701578747</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>41.0</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,58 +7479,58 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.64</v>
+        <v>40.57</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.46</v>
+        <v>42.39</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>16.52</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-171.42</t>
+          <t>-167.48</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,20 +7550,20 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>592.8</t>
+          <t>638.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
@@ -7571,22 +7571,22 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-22.19630447678222</t>
+          <t>-23.50368966397576</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-31.94631315484628</t>
+          <t>-30.69430819354022</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-15.35</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.38</t>
+          <t>-22.43</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.89999999999999</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>40.72</v>
+        <v>40.64</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.52</v>
+        <v>42.46</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-174.37</t>
+          <t>-171.42</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,20 +7980,20 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>446.6</v>
+        <v>565</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>551.6</t>
+          <t>592.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-105</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-20.42357562622512</t>
+          <t>-22.19630447678222</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-72.4510947726103</t>
+          <t>-31.94631315484628</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-15.35</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-11.71</t>
+          <t>-19.04</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-23.38</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>78.79</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>39.89999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>40.83</v>
+        <v>40.72</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.6</v>
+        <v>42.52</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-175.86</t>
+          <t>-174.37</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,20 +8410,20 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>561.2</v>
+        <v>446.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>635.6</t>
+          <t>551.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
@@ -8431,22 +8431,22 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-105</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-10.96402669051872</t>
+          <t>-20.42357562622512</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-69.87038655610866</t>
+          <t>-72.4510947726103</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,42 +8623,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-11.71</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,42 +8754,42 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>78.79</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -8798,29 +8798,29 @@
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>40.96</v>
+        <v>40.83</v>
       </c>
       <c r="AN20" t="n">
-        <v>42.69</v>
+        <v>42.6</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-175.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,20 +8840,20 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>545</v>
+        <v>561.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>635.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
@@ -8861,22 +8861,22 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-10.96402669051872</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-69.87038655610866</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>41.1</v>
+        <v>40.96</v>
       </c>
       <c r="AN21" t="n">
-        <v>42.78</v>
+        <v>42.69</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,20 +9270,20 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>671.6</v>
+        <v>545</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
@@ -9291,22 +9291,22 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>-0.2537794422296447</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-53.93828958410222</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.26</v>
+        <v>41.1</v>
       </c>
       <c r="AN22" t="n">
-        <v>42.87</v>
+        <v>42.78</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-16.28</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-173.99</t>
+          <t>-175.67</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,20 +9700,20 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>620.6</v>
+        <v>671.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>798.1</t>
+          <t>769.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>9.50704058356537</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-35.8857929062109</t>
+          <t>-55.93035499608936</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.89</t>
+          <t>-22.24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.57</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.98999999999999</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.45</v>
+        <v>41.26</v>
       </c>
       <c r="AN23" t="n">
-        <v>42.97</v>
+        <v>42.87</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-15.57</t>
+          <t>-16.28</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-170.98</t>
+          <t>-173.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,20 +10130,20 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1651.024285714286</t>
+          <t>1649.726105563481</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>656.6</v>
+        <v>620.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>993.2</t>
+          <t>798.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
@@ -10151,22 +10151,22 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-336</t>
+          <t>-177</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>31.82121101204554</t>
+          <t>21.40474887077532</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-4.361925888305564</t>
+          <t>-35.8857929062109</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>359.95</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,37 +883,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-8.35</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>24.35</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.38</t>
+          <t>-34.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.46</v>
+        <v>24.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.71</v>
+        <v>24.65</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-65.20</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.35</t>
+          <t>-101.61</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-17.75790910895608</t>
+          <t>-12.48959926035122</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-21.05836437236019</t>
+          <t>16.48610490697548</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1444,22 +1444,22 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1469,17 +1469,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,19 +1488,19 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>24.56</v>
+        <v>24.46</v>
       </c>
       <c r="AN3" t="n">
-        <v>24.72</v>
+        <v>24.71</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-17.1578263337917</t>
+          <t>-17.75790910895608</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.71</v>
+        <v>24.56</v>
       </c>
       <c r="AN4" t="n">
-        <v>24.74</v>
+        <v>24.72</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-16.44863759950652</t>
+          <t>-17.1578263337917</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,43 +2324,43 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.88</v>
+        <v>24.71</v>
       </c>
       <c r="AN5" t="n">
-        <v>24.77</v>
+        <v>24.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.35</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-15.61050545898767</t>
+          <t>-16.44863759950652</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,43 +2754,43 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>24.82</v>
+        <v>24.88</v>
       </c>
       <c r="AN6" t="n">
-        <v>24.8</v>
+        <v>24.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-14.6199856565563</t>
+          <t>-15.61050545898767</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,60 +3179,60 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-7.48</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>24.46</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>26.88</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>11.29</t>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13.44937134459196</t>
+          <t>-14.6199856565563</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,53 +3609,53 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>24.62</v>
+        <v>24.78</v>
       </c>
       <c r="AN8" t="n">
-        <v>24.84</v>
+        <v>24.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,16 +3680,16 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12.06591806681592</t>
+          <t>-13.44937134459196</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.97</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>24.53</v>
+        <v>24.62</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.9</v>
+        <v>24.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,16 +4110,16 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>55.8</v>
+        <v>30.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10.43092782944423</t>
+          <t>-12.06591806681592</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-19.2004612658711</t>
+          <t>-21.05836437236019</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.94</t>
+          <t>-28.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>24.48</v>
+        <v>24.53</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.02</v>
+        <v>24.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,16 +4540,16 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>55.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.836467204639346</t>
+          <t>-10.43092782944423</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-18.96772606853415</t>
+          <t>-19.2004612658711</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>24.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.08</v>
+        <v>25.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>60.26</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
+          <t>-8.836467204639346</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-17.52925699846229</t>
+          <t>-18.96772606853415</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-26.62</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -5339,48 +5339,48 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>24.45</v>
+        <v>24.48</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.11</v>
+        <v>25.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>60.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.89</t>
+          <t>-101.64</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1913.72193877551</t>
+          <t>1910.984719864176</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5.078995254842904</t>
+          <t>-6.994420138476655</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-12.27682771984311</t>
+          <t>-17.52925699846229</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>738</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-12.66</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.05</t>
+          <t>-22.15</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>66.98</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.01000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.4</v>
+        <v>40.39</v>
       </c>
       <c r="AN13" t="n">
-        <v>42.14</v>
+        <v>42.06</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.98</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>41.60</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-146.89</t>
+          <t>-142.24</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>494.0</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>542.8</v>
+        <v>469.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>553.9</t>
+          <t>537.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-30.36588951374844</t>
+          <t>-35.98208213417902</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-50.56319719479484</t>
+          <t>-66.87114154654728</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>494.0</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-14.94</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>40.95</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>40.95</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>41.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-22.81</t>
+          <t>-22.05</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>76.51</t>
+          <t>66.98</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.42</v>
+        <v>40.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.2</v>
+        <v>42.14</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>41.60</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-151.77</t>
+          <t>-146.89</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>494.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>642.2</v>
+        <v>542.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>544.4</t>
+          <t>553.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-26.69365175355818</t>
+          <t>-30.36588951374844</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-51.17459107819161</t>
+          <t>-50.56319719479484</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>494.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-15.77</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-22.81</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>95.56</t>
+          <t>76.51</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>40.47</v>
+        <v>40.42</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.28</v>
+        <v>42.2</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-156.65</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,20 +6690,20 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>677.8</v>
+        <v>642.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>619.5</t>
+          <t>544.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-22.2425718763521</t>
+          <t>-26.69365175355818</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-26.54177551596592</t>
+          <t>-51.17459107819161</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.77</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.56</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.53</v>
+        <v>40.47</v>
       </c>
       <c r="AN16" t="n">
-        <v>42.34</v>
+        <v>42.28</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.12</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>33.89</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-162.21</t>
+          <t>-156.65</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,20 +7120,20 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>658.2</v>
+        <v>677.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>601.6</t>
+          <t>619.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
@@ -7141,22 +7141,22 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-21.46089848733141</t>
+          <t>-22.2425718763521</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-10.22554701578747</t>
+          <t>-26.54177551596592</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.57</v>
+        <v>40.53</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.39</v>
+        <v>42.34</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>33.89</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-167.48</t>
+          <t>-162.21</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,20 +7550,20 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>606</v>
+        <v>658.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>638.8</t>
+          <t>601.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
@@ -7571,22 +7571,22 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>56</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-23.50368966397576</t>
+          <t>-21.46089848733141</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-30.69430819354022</t>
+          <t>-10.22554701578747</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>41.0</t>
         </is>
       </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>40.64</v>
+        <v>40.57</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.46</v>
+        <v>42.39</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>16.52</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-171.42</t>
+          <t>-167.48</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,20 +7980,20 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>592.8</t>
+          <t>638.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-22.19630447678222</t>
+          <t>-23.50368966397576</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-31.94631315484628</t>
+          <t>-30.69430819354022</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-15.35</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.38</t>
+          <t>-22.43</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.89999999999999</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>40.72</v>
+        <v>40.64</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.52</v>
+        <v>42.46</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-174.37</t>
+          <t>-171.42</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,20 +8410,20 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>446.6</v>
+        <v>565</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>551.6</t>
+          <t>592.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
@@ -8431,22 +8431,22 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-105</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-20.42357562622512</t>
+          <t>-22.19630447678222</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-72.4510947726103</t>
+          <t>-31.94631315484628</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-15.35</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-11.71</t>
+          <t>-19.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-23.38</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>78.79</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>39.89999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>40.83</v>
+        <v>40.72</v>
       </c>
       <c r="AN20" t="n">
-        <v>42.6</v>
+        <v>42.52</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-175.86</t>
+          <t>-174.37</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,20 +8840,20 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>561.2</v>
+        <v>446.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>635.6</t>
+          <t>551.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
@@ -8861,22 +8861,22 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-105</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-10.96402669051872</t>
+          <t>-20.42357562622512</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-69.87038655610866</t>
+          <t>-72.4510947726103</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,42 +9053,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-11.71</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,37 +9189,37 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>78.79</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -9228,29 +9228,29 @@
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>40.96</v>
+        <v>40.83</v>
       </c>
       <c r="AN21" t="n">
-        <v>42.69</v>
+        <v>42.6</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-175.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,20 +9270,20 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>545</v>
+        <v>561.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>635.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
@@ -9291,22 +9291,22 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-10.96402669051872</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-69.87038655610866</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.1</v>
+        <v>40.96</v>
       </c>
       <c r="AN22" t="n">
-        <v>42.78</v>
+        <v>42.69</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,20 +9700,20 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>671.6</v>
+        <v>545</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>-0.2537794422296447</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-53.93828958410222</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-22.24</t>
+          <t>-12.71</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-25.57</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.26</v>
+        <v>41.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>42.87</v>
+        <v>42.78</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.28</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-173.99</t>
+          <t>-175.67</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,20 +10130,20 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1649.726105563481</t>
+          <t>1647.918803418803</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>620.6</v>
+        <v>671.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>798.1</t>
+          <t>769.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
@@ -10151,22 +10151,22 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-177</t>
+          <t>-97</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>21.40474887077532</t>
+          <t>9.50704058356537</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-35.8857929062109</t>
+          <t>-55.93035499608936</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>48.18</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.12</t>
+          <t>-32.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,69 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.38</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-6.51</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-1.73</t>
-        </is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-2.68</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.38</v>
+        <v>24.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>24.65</v>
+        <v>24.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-65.20</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
+          <t>-69.11</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.22</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.61</t>
+          <t>-101.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,12 +1092,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -1126,17 +1118,17 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12.48959926035122</t>
+          <t>-10.57152196674195</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>16.48610490697548</t>
+          <t>0.4733927733262249</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.38</t>
+          <t>-34.12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,69 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>35.71</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
+          <t>27.38</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-1.73</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>24.46</v>
+        <v>24.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>24.71</v>
+        <v>24.65</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>-65.20</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.18</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.35</t>
+          <t>-101.61</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,12 +1514,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
@@ -1556,17 +1540,17 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-17.75790910895608</t>
+          <t>-12.57968828311799</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-21.05836437236019</t>
+          <t>4.317991963353279</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1731,11 +1715,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>3629</t>
@@ -1768,7 +1748,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1853,7 +1833,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1879,37 +1859,33 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
+          <t>35.71</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.45</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,30 +1894,26 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.56</v>
+        <v>24.46</v>
       </c>
       <c r="AN4" t="n">
-        <v>24.72</v>
+        <v>24.71</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1960,7 +1932,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1986,12 +1958,12 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-17.1578263337917</t>
+          <t>-15.6519937824764</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-21.05836437236019</t>
+          <t>-17.51112844918866</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -2101,12 +2073,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2161,11 +2133,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>3629</t>
@@ -2198,7 +2166,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2283,7 +2251,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2309,7 +2277,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,24 +2290,20 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.84</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2348,30 +2312,26 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.71</v>
+        <v>24.56</v>
       </c>
       <c r="AN5" t="n">
-        <v>24.74</v>
+        <v>24.72</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2340,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.36</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,7 +2350,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2416,12 +2376,12 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-16.44863759950652</t>
+          <t>-15.31396929761962</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-21.05836437236019</t>
+          <t>-17.51112844918866</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -2531,12 +2491,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2593,7 +2553,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2628,7 +2588,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2598,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-25.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,7 +2673,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2739,7 +2699,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2752,56 +2712,48 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-2.27</t>
-        </is>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1.45</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>24.88</v>
+        <v>24.71</v>
       </c>
       <c r="AN6" t="n">
-        <v>24.77</v>
+        <v>24.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>-0.53</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2762,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.35</t>
+          <t>-101.36</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,7 +2772,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2829,34 +2781,34 @@
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>33.25</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.525</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>122.71</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-15.61050545898767</t>
+          <t>-14.91448581551616</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-21.05836437236019</t>
+          <t>-17.51112844918866</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,7 +2873,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2913,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3023,7 +2975,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3058,7 +3010,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3020,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-24.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,7 +3095,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3169,7 +3121,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3182,56 +3134,48 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
+      <c r="AH7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-2.27</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>24.82</v>
+        <v>24.88</v>
       </c>
       <c r="AN7" t="n">
-        <v>24.8</v>
+        <v>24.77</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3250,7 +3194,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3259,34 +3203,34 @@
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>39.05</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.825</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>123.27</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-14.6199856565563</t>
+          <t>-14.44236897303025</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-21.05836437236019</t>
+          <t>-17.5773015463919</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3391,12 +3335,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3453,7 +3397,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3488,7 +3432,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3442,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,7 +3517,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3599,7 +3543,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,59 +3553,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.67</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1.95</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>24.78</v>
+        <v>24.82</v>
       </c>
       <c r="AN8" t="n">
-        <v>24.81</v>
+        <v>24.8</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.62</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3680,7 +3616,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3689,34 +3625,34 @@
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>41.15</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57.675</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>123.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13.44937134459196</t>
+          <t>-13.87238123241904</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-21.05836437236019</t>
+          <t>-18.59764520145394</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,7 +3717,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3821,12 +3757,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3881,11 +3817,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>3629</t>
@@ -3893,12 +3825,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,7 +3850,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3860,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-40.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +3935,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,7 +3961,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,59 +3971,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.33</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
+          <t>16.67</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-1.27</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>24.62</v>
+        <v>24.78</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.84</v>
+        <v>24.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.85</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4024,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4034,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>30.8</v>
+        <v>37.75</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63.175</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>122.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12.06591806681592</t>
+          <t>-13.01324232895815</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-21.05836437236019</t>
+          <t>-19.76607738006206</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,7 +4135,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4251,12 +4175,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4200,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4311,11 +4235,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>3629</t>
@@ -4323,12 +4243,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4258,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4268,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4278,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4343,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-28.97</t>
+          <t>-28.38</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4353,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,69 +4379,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>24.53</v>
+        <v>24.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>24.9</v>
+        <v>24.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>19.98</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4442,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4452,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>55.8</v>
+        <v>30.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>123.09</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-42</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10.43092782944423</t>
+          <t>-11.78545413784835</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-19.2004612658711</t>
+          <t>-20.27397772878574</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4508,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4553,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4563,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4593,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4618,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4655,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,7 +4665,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4768,7 +4680,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4690,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4700,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4765,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.94</t>
+          <t>-28.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,7 +4775,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4873,7 +4785,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4801,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,59 +4811,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>66.67</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.17</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.6</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>24.48</v>
+        <v>24.53</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.02</v>
+        <v>24.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>46.87</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.16</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4864,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4874,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>55.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>131.41</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.836467204639346</t>
+          <t>-10.24208621222337</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-18.96772606853415</t>
+          <t>-18.80226473664864</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4930,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,7 +4985,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5015,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5040,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5077,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5087,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5102,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5112,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5122,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-32.10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5187,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.62</t>
+          <t>-27.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5197,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,69 +5223,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.25</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>24.48</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.08</v>
+        <v>25.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>60.26</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
+          <t>46.87</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.17</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5286,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.64</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5296,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1910.984719864176</t>
+          <t>1907.862711864407</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.13333333333334</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>132.77</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6.994420138476655</t>
+          <t>-8.685690116873324</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-17.52925699846229</t>
+          <t>-19.13545100728678</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5352,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5397,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5407,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5437,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>756</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5462,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5499,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,7 +5509,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5648,7 +5544,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.66</t>
+          <t>-30.85</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,7 +5619,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -5733,7 +5629,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5754,64 +5650,56 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>60.32</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
+          <t>65.73</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.35</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>41.01000000000001</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.39</v>
+        <v>40.38</v>
       </c>
       <c r="AN13" t="n">
-        <v>42.06</v>
+        <v>41.99</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>42.93</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>44.07</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
+          <t>46.11</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.44</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5820,7 +5708,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.24</t>
+          <t>-137.87</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5718,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>254.0</t>
+          <t>260.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>469.8</v>
+        <v>347.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>537.9</t>
+          <t>503.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>731.15</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-68</t>
+          <t>-155</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-35.98208213417902</t>
+          <t>-41.27109452626673</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-66.87114154654728</t>
+          <t>-75.69130956011514</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>254.0</t>
+          <t>260.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,7 +5819,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5859,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5884,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6033,7 +5921,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +5931,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +5946,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +5956,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +5966,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-12.66</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6031,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-22.05</t>
+          <t>-22.15</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6041,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6184,64 +6072,56 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>66.98</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
+          <t>60.32</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.54</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.01000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.4</v>
+        <v>40.39</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.14</v>
+        <v>42.06</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>41.60</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
+          <t>44.07</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0.49</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6250,7 +6130,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-146.89</t>
+          <t>-142.24</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6140,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>494.0</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>542.8</v>
+        <v>469.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>553.9</t>
+          <t>537.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>731.55</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-68</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-30.36588951374844</t>
+          <t>-35.01287361102156</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-50.56319719479484</t>
+          <t>-66.33651717460953</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>494.0</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6196,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-14.94</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6241,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6251,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6281,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6306,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>40.95</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>40.95</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>41.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6343,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6353,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6368,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6378,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6388,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6453,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-22.81</t>
+          <t>-22.05</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6463,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6614,264 +6494,256 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>76.51</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
+          <t>66.98</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.46</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
+          <t>40.98999999999999</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>43.03</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>41.60</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-146.89</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>1646.129445234708</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>494.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>542.8</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>553.9</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>750.51</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-29.31766569036921</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-49.96050958193689</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>494.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/05/28</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-14.94</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>誠品生活</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>5.61175015634552</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>2.720079552075342</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>2.597352307479901</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>36.81</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>48.18</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>354.9</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>誠品生活-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
           <t>40.95</t>
         </is>
       </c>
-      <c r="AM15" t="n">
-        <v>40.42</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>43.07</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>37.75</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-151.77</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>1647.918803418803</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>273.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>642.2</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>544.4</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-26.69365175355818</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-51.17459107819161</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>273.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/05/28</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>-15.77</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>誠品生活</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>誠品生活</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>5.61175015634552</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>2.720079552075342</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>2.597352307479901</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>48.18</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>38.48%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>0.68%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>358.35</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>1941</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>全通路銷售服務68.56%、餐旅服務24.51%、其他6.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>誠品生活-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>文化創意業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6765,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6775,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6790,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6800,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6810,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +6875,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-22.81</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +6885,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7044,64 +6916,56 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>95.56</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
+          <t>76.51</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.32</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.47</v>
+        <v>40.42</v>
       </c>
       <c r="AN16" t="n">
-        <v>42.28</v>
+        <v>42.2</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>39.22</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
+          <t>37.75</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0.6</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -7110,7 +6974,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-156.65</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +6984,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>677.8</v>
+        <v>642.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>619.5</t>
+          <t>544.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>741.51</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-22.2425718763521</t>
+          <t>-25.56442134644782</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-26.54177551596592</t>
+          <t>-50.49619482162086</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7040,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.77</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7085,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7095,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7125,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7150,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7187,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7197,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7212,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7222,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7433,7 +7297,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7307,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,64 +7338,56 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
+          <t>95.56</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.04</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.53</v>
+        <v>40.47</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.34</v>
+        <v>42.28</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.12</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>33.89</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0.66</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7540,7 +7396,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-162.21</t>
+          <t>-156.65</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7406,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>658.2</v>
+        <v>677.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>601.6</t>
+          <t>619.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>743.17</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-21.46089848733141</t>
+          <t>-21.03137162368908</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-10.22554701578747</t>
+          <t>-25.77945249182596</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7462,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7507,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7547,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,7 +7572,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7726,12 +7582,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7609,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7619,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7634,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7644,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7654,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7719,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7729,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7912,56 +7768,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
+      <c r="AH18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.37</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>40.57</v>
+        <v>40.53</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.39</v>
+        <v>42.34</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
+          <t>33.89</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.72</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7970,7 +7818,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-167.48</t>
+          <t>-162.21</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7828,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>606</v>
+        <v>658.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>638.8</t>
+          <t>601.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>744.35</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>56</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-23.50368966397576</t>
+          <t>-20.16808419311874</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-30.69430819354022</t>
+          <t>-9.370554431696632</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +7884,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +7929,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +7939,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +7969,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +7994,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>41.0</t>
         </is>
       </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8181,11 +8029,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>2926</t>
@@ -8193,12 +8037,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8052,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8062,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8072,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8137,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8147,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8339,59 +8183,51 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>93.94</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.41</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>40.64</v>
+        <v>40.57</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.46</v>
+        <v>42.39</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>16.52</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0.78</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8400,7 +8236,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-171.42</t>
+          <t>-167.48</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8246,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>592.8</t>
+          <t>638.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>749.91</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-22.19630447678222</t>
+          <t>-22.13127142246821</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-31.94631315484628</t>
+          <t>-29.73746597323702</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>991.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8302,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-15.35</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8347,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8551,7 +8387,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8412,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8611,11 +8447,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>2926</t>
@@ -8623,12 +8455,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8470,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8480,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8490,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8555,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.38</t>
+          <t>-22.43</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8565,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8769,59 +8601,51 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>86.36</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-2.00</t>
-        </is>
+          <t>93.94</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-1</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.89999999999999</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>40.72</v>
+        <v>40.64</v>
       </c>
       <c r="AN20" t="n">
-        <v>42.52</v>
+        <v>42.46</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>7.98</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.87</t>
-        </is>
+          <t>16.52</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-0.83</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8830,7 +8654,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-174.37</t>
+          <t>-171.42</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8664,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>446.6</v>
+        <v>565</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>551.6</t>
+          <t>592.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>742.0700000000001</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-105</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-20.42357562622512</t>
+          <t>-20.74832695869206</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-72.4510947726103</t>
+          <t>-30.87814439067915</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>451.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8720,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-15.35</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8765,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8805,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +8830,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9041,11 +8865,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>2926</t>
@@ -9053,12 +8873,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +8888,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +8898,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +8908,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-11.71</t>
+          <t>-19.04</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +8973,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-23.38</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +8983,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9194,64 +9014,56 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>78.79</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-2.68</t>
-        </is>
+          <t>86.36</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-2</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>39.73999999999999</t>
+          <t>39.89999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>40.83</v>
+        <v>40.72</v>
       </c>
       <c r="AN21" t="n">
-        <v>42.6</v>
+        <v>42.52</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-0.87</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9260,7 +9072,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-175.86</t>
+          <t>-174.37</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9082,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>561.2</v>
+        <v>446.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>635.6</t>
+          <t>551.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>739.17</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-74</t>
+          <t>-105</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-10.96402669051872</t>
+          <t>-18.90654197105804</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-69.87038655610866</t>
+          <t>-71.26203697307199</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>451.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9138,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-16.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9183,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9193,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9223,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9248,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9471,11 +9283,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>2926</t>
@@ -9483,42 +9291,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>40.05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-11.71</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9391,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-23.86</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9401,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9624,32 +9432,28 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>51.52</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-2.98</t>
-        </is>
+          <t>78.79</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-2.68</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -9658,30 +9462,26 @@
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>40.96</v>
+        <v>40.83</v>
       </c>
       <c r="AN22" t="n">
-        <v>42.69</v>
+        <v>42.6</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-3.02</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-0.88</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9690,7 +9490,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-176.24</t>
+          <t>-175.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9500,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>545</v>
+        <v>561.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>668.8</t>
+          <t>635.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>743.53</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-123</t>
+          <t>-74</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-0.2537794422296447</t>
+          <t>-9.387361061600965</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-53.93828958410222</t>
+          <t>-68.55109648459495</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9556,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.91</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9601,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9841,7 +9641,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9876,12 +9676,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9713,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9948,7 +9748,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-12.71</t>
+          <t>-18.51</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10023,17 +9823,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10059,59 +9859,51 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>25.76</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-3.22</t>
-        </is>
+          <t>51.52</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-2.98</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.73999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.1</v>
+        <v>40.96</v>
       </c>
       <c r="AN23" t="n">
-        <v>42.78</v>
+        <v>42.69</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-8.85</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>-0.89</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -10120,7 +9912,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-175.67</t>
+          <t>-176.24</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +9922,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1647.918803418803</t>
+          <t>1646.129445234708</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>671.6</v>
+        <v>545</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>769.4</t>
+          <t>668.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>749.71</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-97</t>
+          <t>-123</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>9.50704058356537</t>
+          <t>1.369681742579761</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-55.93035499608936</t>
+          <t>-52.4800709123208</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10231,7 +10023,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10271,7 +10063,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,17 +10088,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/創意生活產業.xlsx
+++ b/Result/checksun_type/創意生活產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-3.08</v>
+        <v>-1.92</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2.68</v>
+        <v>-3.63</v>
       </c>
       <c r="AJ2" t="inlineStr">